--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -94,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,13 +111,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -485,12 +495,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +524,8 @@
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -576,150 +590,381 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Sweep</t>
+          <t>Source-organism category</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>What it searched</t>
+          <t>Datasets</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Venue coverage</t>
+          <t>Variants</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Papers</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Example proteins</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>First sweep</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>"machine learning guided enzyme engineering" (+/- organism)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>nature.com, 2025</t>
+          <t>Bacteria</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>93517</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, LbCas12a, creatinase</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Second sweep</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Same query, organism clause dropped</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Springer Nature via Europe PMC, 2025</t>
+          <t>Archaea</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1753</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>ParLQ, PylRS (IFRS), pCNFRS, Tgo-D4K polymerase</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Third sweep</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>"deep mutational scanning" / "variant effect map" / "massively parallel mutagenesis" / "site-saturation mutagenesis"</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>All publishers via Europe PMC, 2025, open access</t>
+          <t>Yeast / fungi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>118603</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>RNA Pol II Rpb1 (S. cerevisiae)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Fourth sweep (ACS)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Title/abstract screen</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025</t>
+          <t>Plants</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>419</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>AtHMT, CONSTANS (A. thaliana)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Fifth sweep (PNAS)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Title-matched + abstract-matched protein/enzyme engineering terms</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>PNAS, 2025, open access</t>
+          <t>Viruses (incl. bacteriophage)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>270545</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>TEV protease, influenza NEP, T7 RNA polymerase, Con1 (designed potyviral consensus)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Sixth sweep (Cell Press)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Title-matched</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Cell, Mol Cell, Cell Chem Biol, Cell Systems, Structure, Cell Host &amp; Microbe, Immunity, Curr Biol, Chem, iScience, Cell Rep Methods, Cell Rep Phys Sci</t>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>61070</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>MET kinase domain, SHP2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>Other (animal-derived)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>VHH nanobody, camelid-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Subtotal: Prokaryotes (Bacteria + Archaea)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>95270</v>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Subtotal: Eukaryotes, non-human (Yeast/fungi + Plants + Other)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>119080</v>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B21" s="7">
+        <f>SUM(B12:B18)</f>
+        <v/>
+      </c>
+      <c r="C21" s="7">
+        <f>SUM(C12:C18)</f>
+        <v/>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>'Papers' counts distinct DOIs within that category; a paper spanning several organisms (e.g. Jiang 2024/PRIME, which has datasets on a bacterium, an archaeon, a bacteriophage and a camelid nanobody) is counted once per category it touches, so the Papers column does not sum to 16. Datasets and Variants do sum exactly to the Curated tab's totals -- every dataset has exactly one source_organism. 'Other (animal-derived)' is the VHH nanobody dataset, filed under datasets/ even though a camelid is not a bacterium, archaeon, yeast or plant -- the branch has no separate tree for it yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sweep</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>What it searched</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Venue coverage</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>First sweep</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>"machine learning guided enzyme engineering" (+/- organism)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>nature.com, 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Second sweep</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Same query, organism clause dropped</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Springer Nature via Europe PMC, 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Third sweep</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>"deep mutational scanning" / "variant effect map" / "massively parallel mutagenesis" / "site-saturation mutagenesis"</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>All publishers via Europe PMC, 2025, open access</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Fourth sweep (ACS)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Title/abstract screen</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Fifth sweep (PNAS)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Title-matched + abstract-matched protein/enzyme engineering terms</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>PNAS, 2025, open access</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Sixth sweep (Cell Press)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Title-matched</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Cell, Mol Cell, Cell Chem Biol, Cell Systems, Structure, Cell Host &amp; Microbe, Immunity, Curr Biol, Chem, iScience, Cell Rep Methods, Cell Rep Phys Sci</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>"directed evolution" / "site-saturation mutagenesis" / "laboratory evolution" / "yeast surface display"+"deep sequencing", explicitly excluding "deep mutational scanning" and "enzyme engineering" phrasing</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>All publishers via Europe PMC, 2025, journals only (no bioRxiv)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>See the 'Curated' tab for shipped datasets with variant counts, 'Rejected' for every paper chased to a documented reason, and 'Open (maybes)' for leads left for a future session. Full narrative detail, including access routes and per-sweep notes, is in candidates_2025.md on the 2025 branch.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A20:C20"/>
+  <mergeCells count="3">
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -799,711 +1044,711 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Zhang</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Machine learning-guided evolution of pyrrolysyl-tRNA synthetase for improved incorporation efficiency of diverse noncanonical amino acids</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-61952-2</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="9" t="n">
         <v>508</v>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>IFRS (PylRS variant); FFT-PLSR-guided rounds rebased onto one scale</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Data-driven protease engineering by DNA-recording and epistasis-aware machine learning</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-60622-7</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>datasets_virus</t>
         </is>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="9" t="n">
         <v>268446</v>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>TEV protease (MLDEEP); one dataset per P1' substrate residue plus a full saturation scan</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Duan</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Widespread epistasis shapes RNA polymerase II active site function and evolution</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-63304-6</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="9" t="n">
         <v>118603</v>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>RNA Pol II Rpb1 trigger loop, S. cerevisiae; growth fitness across selective conditions</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Landwehr</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Accelerated enzyme engineering by machine-learning guided cell-free expression</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-024-55399-0</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="9" t="n">
         <v>10909</v>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>McbA amide synthetase; conversion of 9 pharmaceuticals</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Yang</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Active learning-assisted directed evolution</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-55987-8</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="9" t="n">
         <v>790</v>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>ParLQ; diastereoselectivity and yield on a non-native cyclopropanation (ALDE)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Singh</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>A generalized platform for artificial intelligence-powered autonomous enzyme engineering</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-61209-y</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="9" t="n">
         <v>176</v>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>AtHMT methyltransferase, substrate preference</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Zhang</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Integrating protein language models and automatic biofoundry for enhanced protein evolution</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-56751-8</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="9" t="n">
         <v>384</v>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>pCNFRS tRNA synthetase; 4 rounds of ESM-2-nominated variants</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Silverstein</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Custom CRISPR-Cas9 PAM variants via scalable engineering and machine learning</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41586-025-09021-y</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="9" t="n">
         <v>68992</v>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>PAMmla; ~1,078 SpCas9 variants per dataset, PAM specificity</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Alamos</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Nat Biotechnol</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Multiplexed profiling of transcriptional regulators in plant cells</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41587-025-02880-w</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="9" t="n">
         <v>243</v>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>CONSTANS activation domain (ENTRAP-seq); tile libraries out of scope, single-substitution table only</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Jiang</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="9" t="n">
         <v>2024</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Sci Adv</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>A general temperature-guided language model to design proteins of enhanced stability and activity</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>10.1126/sciadv.adr2641</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>datasets + datasets_virus</t>
         </is>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="9" t="n">
         <v>353</v>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>PRIME platform; Tgo-D4K polymerase, VHH nanobody, LbCas12a, creatinase, T7 RNA polymerase</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Estevam</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>eLife</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Mapping kinase domain resistance mechanisms for the MET receptor tyrosine kinase via deep mutational scanning</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>10.7554/eLife.101882</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>datasets_human</t>
         </is>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="9" t="n">
         <v>44889</v>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>MET kinase domain; one dataset per inhibitor plus DMSO control</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Jiang</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Deep mutational scanning of the multi-domain phosphatase SHP2 reveals mechanisms of regulation and pathogenicity</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-60641-4</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>datasets_human</t>
         </is>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="9" t="n">
         <v>16181</v>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>SHP2 full-length and isolated PTP domain; yeast growth-rescue enrichment</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Wysocki</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="9" t="n">
         <v>2026</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>ACS Synth Biol</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>High-Throughput Detection of Cyanobacterial Form I Rubisco Assembly</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>10.1021/acssynbio.5c00591</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="9" t="n">
         <v>13216</v>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>RbcL (H. neapolitanus); phage-selection site-saturation, with/without GroELS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Thornton</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>ACS Synth Biol</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Cell-Free Protein Synthesis as a Method to Rapidly Screen Machine Learning-Generated Protease Variants</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>10.1021/acssynbio.5c00062</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>datasets_virus</t>
         </is>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Con1, a designed consensus potyviral protease; region A and B site-saturation</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Teo</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Cell Rep</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Probing the functional constraints of influenza A virus NEP by deep mutational scanning</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>10.1016/j.celrep.2024.115196</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>datasets_virus</t>
         </is>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="9" t="n">
         <v>1894</v>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Influenza A NEP, A/WSN/1933 strain; found via title sweep, data was on Zenodo not in the article supplement</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Wong</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="9" t="n">
         <v>2025</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Nat Commun</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Characterizing and engineering post-translational modifications with high-throughput cell-free expression</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-60526-6</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>datasets</t>
         </is>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="9" t="n">
         <v>285</v>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>CjPglB oligosaccharyltransferase; 15-position site-saturation, AlphaLISA glycosylation signal</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -1514,11 +1759,11 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="8">
+      <c r="H18" s="10">
         <f>SUM(H2:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="10">
         <f>SUM(I2:I17)</f>
         <v/>
       </c>
@@ -1573,1350 +1818,1350 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>iCASE 2025, thermostability/activity tailoring</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-55944-5</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Second sweep</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>No work item reaches the 20-variant floor. 63-sheet Source Data workbook; every sheet with mutant labels holds at most 16 rows; the large sheets are simulation output (DSI, compressibility, binding free energy), not experimental measurement.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Artificial metathase (de novo + directed evolution)</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41929-025-01436-0</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Second sweep</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>No variant table. One spreadsheet per figure, 4-38 rows each of kinetics/titration data, none a per-variant list.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Kemp eliminase distal mutations (3 de novo enzymes)</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-63802-7</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Second sweep</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>No variant table. Four sheets of kinetic traces / stopped-flow raw data, no mutant-labelled block.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>ML prediction-tool papers evaluated on others' data (CatPred, CataPro, TopEC, PreMode, DeepMVP, ABACUS-T, LassoESM, cross-attention specificity GNN, biophysics-based PLMs)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>(various, not individually recorded)</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Second sweep</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Phase 1 exclusion: a dataset a paper merely evaluates on belongs to whoever measured it, not to the modeling paper.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>AI-designed base/prime editors</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41586-025-09298-z</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Second sweep</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>AI-designed editors are not variants of one wild type.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Reviews/perspectives bundle (ML applied to biocatalysis, PET hydrolase standardisation guidelines, C1 utilisation)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>(not recorded)</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Second sweep</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Reviews, not primary measurement papers.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>DMS in E. coli periplasm (human A-beta-42 amyloid propensity)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>10.1073/pnas.2516165122</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Assay host is bacterial but the protein is human (A-beta-42); readout is aggregation propensity via a bacterial reporter, not enzyme fitness. Deprioritized to datasets_human/ scope, not chased further.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Reshaping a glycoside hydrolase active site (330,000-clone droplet sort)</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>10.1021/acscentsci.5c01227</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Only a handful of named winners (M1, M2, ...) individually characterised; no systematic per-variant table in the paper or its PDF-only supplement.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Deep Mutational Scanning of FDX1</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-67869-0</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>FigShare deposit holds only raw Enrich2-style per-sample counts (2.1 GB), not scores. Source Data has only anonymized score distributions and position-averaged values, no per-variant readout.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>EGFR resistance to 4th-generation TKIs</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41698-025-01086-2</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Same experimental shape as the curated MET paper, but no GitHub deposit. Data availability names only raw GEO reads; the PDF-only supplement holds FEP calculations for a handful of representative isoforms, not a per-variant table.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Glucokinase variant characterization</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>10.3390/ijms27010156</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>25 individually chosen clinical variants, well under the floor; not a saturation library.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Directed evolution of a beta-lactamase (conformational states)</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>10.1002/pro.70322</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>3 successive mutants + WT, well under the floor.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Deep structure-function analysis of Mus81 (dominant mutational scanning)</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>10.1073/pnas.2506043122</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Deposited data is a binary Y/N hit classification (dominant / fails-to-complement), not a quantitative per-variant score; graded growth-sensitivity data not deposited.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Pyranose oxidase oligomerization engineering</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>10.1111/febs.70004</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Zenodo deposit is models/docking scores only; experimental data available upon request.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Isophthalate dioxygenase engineering</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>10.1128/jb.00221-25</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>No data-availability statement found.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Confocal absorbance-activated droplet sorting (cAADS)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>10.1002/advs.202505324</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Third sweep</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Data available from the corresponding author upon reasonable request.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Directed evolution of a plant Rubisco chaperone</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>10.1073/pnas.2510701122</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Third + fifth sweep</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>PDF-only SI; text says 'selected' variants, not a full library table.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>In vivo directed evolution of an ultrafast Rubisco</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>10.1073/pnas.2505083122</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Third + fifth sweep</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Kinetic characterisation covers only ~7 named substitutions; the 292-row dataset is population allele-frequency trajectories per locus across evolution rounds, not per-clone genotype-fitness pairs.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Directed evolution of a covalent RNA-labeling tag</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>10.1073/pnas.2422085122</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Third + fifth sweep</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>PDF-only SI.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Nanobody-antigen interface optimisation</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>10.1073/pnas.2426438122</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Third + fifth sweep</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>PDF-only SI; phage display down to a small validated set.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>PET hydrolases from natural diversity</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>(not recorded)</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Fourth sweep (ACS)</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Homolog panel of ~400 distinct natural sequences, no shared wild type.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>KdcA directed evolution</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>(not recorded)</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Fourth sweep (ACS)</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>PDF-only supplement; text names one 8-substitution final variant, not a library table.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>DyP peroxidase thermostability</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>(not recorded)</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Fourth sweep (ACS)</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>PDF-only supplement, a handful of designed variants.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>SPOT metallopeptide library</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>(not recorded)</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Fourth sweep (ACS)</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>PDF-only supplement, small named set.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n">
+      <c r="A26" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>F. rodentium Cas9 (structural/cryo-EM)</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>(not recorded)</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Sixth sweep (Cell Press)</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Not chased further -- likely a handful of validated point mutants, no data-availability statement found.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>ODM protein-design pipeline</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>(not recorded)</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Sixth sweep (Cell Press)</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Not chased further -- generative-model paper, likely benchmarks on public data (Phase 1 evaluated-on exclusion).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n">
+      <c r="A28" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Chen 2025, Cas12a variant profiling</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-57150-9</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>'Variants' are 24 orthologs, and activity varies per target sequence, not per protein substitution -- no single wild-type to normalise against.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Zhu 2025, DropAI droplet screening</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-58139-0</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>ML optimises the cell-free reaction composition, not protein sequence.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>m6A-IIN modification-site prediction</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>10.1038/s42003-025-08265-8</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>RNA modification sites, no protein variants.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Nanozymes review</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-62063-8</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Review.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>CRISPR-Cas in agriculture</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41580-025-00834-3</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Review.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n">
+      <c r="A33" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>CRISPR single-nucleotide diagnostics</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>10.1038/s43856-025-00933-4</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Review.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
+      <c r="A34" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>One-carbon biochemicals</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>10.1038/s44160-025-00835-2</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Review.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n">
+      <c r="A35" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Antimicrobial peptides</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41579-025-01200-y</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Review.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Protein folding and proteostasis</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41392-025-02439-w</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Review.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Non-CG DNA methylation</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41588-025-02303-1</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Review.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Antibacterial preclinical pipeline</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41579-025-01167-w</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Review.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n">
+      <c r="A39" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>African bioeconomy genomics</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>10.1038/s44185-025-00102-9</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Perspective.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n">
+      <c r="A40" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Seven technologies to watch in 2025</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>10.1038/d41586-025-00075-6</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>News feature.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n">
+      <c r="A41" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>ESHG 2025 ePoster abstracts</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41431-025-01934-6</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Rejected list (early sweeps)</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Conference abstracts.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n">
+      <c r="A42" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Wong (chitosanase, signal peptide optimization)</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>10.1021/acs.jafc.5c13730</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Iterative rounds to one named winner (M8); paywalled, not opened past the abstract.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n">
+      <c r="A43" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>PROTEUS mammalian directed-evolution platform</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41467-025-59438-2</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Methods/tool paper; the 'N variants' figures are allele-frequency spectra from continuous passaging, not an isolated-clone table; the two characterized Nb139 mutations are far under floor.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n">
+      <c r="A44" s="11" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>Golden Gate continuous-evolution toolkit</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>10.1093/synbio/ysaf014</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Pure toolkit demonstration; no target-protein dataset, just proof the mutator works.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n">
+      <c r="A45" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Maize HPPD via TADR</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>10.1111/pbi.70160</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>3-page technical advance; 9 point mutants individually tested, qualitative colony-color readout for most.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n">
+      <c r="A46" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>MerR Hg2+ biosensor</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>10.1016/j.bios.2025.117687</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Selection funnel (98% eliminated, then top 0.2%) ending in one named variant (V124E); not open access.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n">
+      <c r="A47" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>Oncolytic Sindbis virus (osteosarcoma)</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>10.1016/j.omton.2025.201096</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Adaptive passaging to a consensus lineage, not a mapped substitution landscape; 'variant' appears 6 times in the whole paper.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n">
+      <c r="A48" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>Rubisco laboratory-evolution screen (Nat Plants)</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>10.1038/s41477-025-02093-8</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Screen narrows to exactly two named point mutations (M116L, A242V), deeply characterized but not a library table.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="n">
+      <c r="A49" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Nonheme iron BsQueD (alkene amination)</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>10.1021/jacsau.5c00817</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>'An optimized variant' -- lineage evolution to one champion.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n">
+      <c r="A50" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>PchB to chorismate mutase (reverse evolution)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>10.1021/acs.biochem.5c00157</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Functional-complementation selection from a 7-position, 38,000-variant library down to a handful of named sequenced clones; no per-variant table, just individually characterized survivors.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="n">
+      <c r="A51" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>PHL7 PET hydrolase (4 rounds)</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>10.1016/j.checat.2025.101399</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Four named final variants (Jemez, Santa Fe, Taos, Tusas); no deposited dataset, 'available upon reasonable request'.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="n">
+      <c r="A52" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Q-body immunosensor quenching prediction</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>10.1021/jacsau.4c01189</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>The large NGS-scored library is a synthetic nanobody repertoire, not point mutants of one wild type; validated point-mutant sets (Trp scans) are single digits per antibody.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="n">
+      <c r="A53" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Curr Protoc SELIS walkthrough</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>10.1002/cpz1.70218</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Protocol demonstration, not a dataset paper.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n">
+      <c r="A54" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Ebola VP40 patient mutations</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>10.1016/j.jbc.2025.110489</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>'40 mutations' is epidemiological surveillance across outbreak lineages, not an experimental library; only 2 mutations (R204H, H269R) are lab-characterized.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="n">
+      <c r="A55" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Affibody stability (DR5 / TNFR1)</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>10.1002/bit.28954</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>Deep sequencing used only to triage candidates for individual validation; reported data is a handful of purified variants, not library-wide.</t>
         </is>
@@ -2977,90 +3222,90 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Class A beta-lactamase gatekeeper-residue screen (5 enzymes)</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>10.1016/j.jbc.2025.110347</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Genuine deep-sequencing fitness data in a legacy .xls (needs xlrd): site saturation of Ambler position 105 in BlaC, CTX-M-14, KPC-2, NmcA, TEM-1, each vs. 7 substrates/inhibitors, 3 replicates, raw counts and per-replicate fitness values -- not just a figure.</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Single saturated position per enzyme: 19 substitutions + WT, one row under this branch's usual floor. Worth a second look if the bar is 'genuine deep-sequencing data' rather than 'library-scale'.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Tryptophan decarboxylase (TDC) active-site recombination (SUMS)</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>10.1002/pro.70356</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Substrate-multiplexed screening across 5 active-site positions; a clean prior single-site-saturation sub-library (96 unique single mutants) plus iterative combinatorial recombination libraries (~250 variants total, up to triple mutants, LC-MS-quantified). Multi-site labels are within format scope.</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Data availability is 'upon reasonable request' -- nothing machine-readable found in the supplement. Needs an email to the authors.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Yeast-display A-beta-fibril conformational antibody campaign</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>10.3389/fimmu.2025.1655893</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Real NGS sort-round data deposited on GitHub (Tessier-Lab-UMich/druglike-abeta-antibodies): CDR-sequence frequency tables for a defined 10-site NNK library (5 in HCDR1, 5 in LCDR2) built off a named parent antibody ('clone 97').</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Needs clone 97's parent CDR sequence from a different, earlier paper, and working out which numbered file per replicate is 'before' vs. 'after' selection -- not safe to guess at.</t>
         </is>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -893,12 +893,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Title/abstract screen</t>
+          <t>No single boolean query recorded (unlike the other sweeps) -- browsed each journal's 2025 issue listings directly, then read title and abstract of anything protein/enzyme-shaped. Direct ACS access returns a 403 on articles and supplements, so retrieval for anything that looked promising went through Europe PMC instead.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025</t>
+          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025, open access</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Title-matched + abstract-matched protein/enzyme engineering terms</t>
+          <t>Two separate matches, then deduped: title-matched on protein/enzyme-engineering terms (30 hits) and abstract-matched on landscape/library terms ("fitness landscape", "combinatorial library", etc., 11 hits) -- 41 unique papers total.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Title-matched</t>
+          <t>Title-matched across the full journal family (43 hits) -- almost entirely clinical-ML iScience papers with no connection to protein engineering, so no separate abstract pass was run.</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>545965</v>
+        <v>546125</v>
       </c>
     </row>
     <row r="7">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -621,17 +621,17 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>93517</v>
+        <v>93677</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, LbCas12a, creatinase</t>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, creatinase</t>
         </is>
       </c>
     </row>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>95270</v>
+        <v>95430</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -811,7 +811,7 @@
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>'Papers' counts distinct DOIs within that category; a paper spanning several organisms (e.g. Jiang 2024/PRIME, which has datasets on a bacterium, an archaeon, a bacteriophage and a camelid nanobody) is counted once per category it touches, so the Papers column does not sum to 16. Datasets and Variants do sum exactly to the Curated tab's totals -- every dataset has exactly one source_organism. 'Other (animal-derived)' is the VHH nanobody dataset, filed under datasets/ even though a camelid is not a bacterium, archaeon, yeast or plant -- the branch has no separate tree for it yet.</t>
+          <t>'Papers' counts distinct DOIs within that category; a paper spanning several organisms (e.g. Jiang 2024/PRIME, which has datasets on a bacterium, an archaeon, a bacteriophage and a camelid nanobody) is counted once per category it touches, so the Papers column does not sum to the 17-paper total. Datasets and Variants do sum exactly to the Curated tab's totals -- every dataset has exactly one source_organism. 'Other (animal-derived)' is the VHH nanobody dataset, filed under datasets/ even though a camelid is not a bacterium, archaeon, yeast or plant -- the branch has no separate tree for it yet.</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Fourth sweep (ACS)</t>
+          <t>Fourth sweep (ACS) -- SUPERSEDED</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>No single boolean query recorded (unlike the other sweeps) -- browsed each journal's 2025 issue listings directly, then read title and abstract of anything protein/enzyme-shaped. Direct ACS access returns a 403 on articles and supplements, so retrieval for anything that looked promising went through Europe PMC instead.</t>
+          <t>No single boolean query recorded (unlike the other sweeps) -- browsed each journal's 2025 issue listings directly, then read title and abstract of anything protein/enzyme-shaped. Direct ACS access returns a 403 on articles and supplements, so retrieval went through Europe PMC. Redone systematically as the seventh sweep below, which found a paper this pass missed.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -939,22 +939,39 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Seventh sweep (ACS, redone)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>The fourth sweep redone as a real query for parity with the others: JOURNAL:(5 ACS titles) AND PUB_YEAR:2025 AND SRC:MED AND (deep mutational scanning OR site-saturation mutagenesis OR directed evolution OR variant effect map OR massively parallel mutagenesis OR enzyme engineering OR protein engineering, as quoted phrases) -- 237 hits, 234 unseen; all 234 abstracts pulled and keyword-scored for per-variant-table signals. Found Somvilla 2025, which the manual pass had missed.</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>"directed evolution" / "site-saturation mutagenesis" / "laboratory evolution" / "yeast surface display"+"deep sequencing", explicitly excluding "deep mutational scanning" and "enzyme engineering" phrasing</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>All publishers via Europe PMC, 2025, journals only (no bioRxiv)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>See the 'Curated' tab for shipped datasets with variant counts, 'Rejected' for every paper chased to a documented reason, and 'Open (maybes)' for leads left for a future session. Full narrative detail, including access routes and per-sweep notes, is in candidates_2025.md on the 2025 branch.</t>
         </is>
@@ -964,7 +981,7 @@
   <mergeCells count="3">
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -976,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1748,26 +1765,70 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Somvilla</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ACS Catalysis</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Ultrahigh-Throughput Activity Engineering of Promiscuous Amidases through a Fluorescence-Activated Cell Sorting Assay</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c01903</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>datasets</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>SaAmd amidase (Sphingomonas alpina); one dataset per substrate across 8 amide/ester/carbamate substrates</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="10">
-        <f>SUM(H2:H17)</f>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="10">
+        <f>SUM(H2:H18)</f>
         <v/>
       </c>
-      <c r="I18" s="10">
-        <f>SUM(I2:I17)</f>
+      <c r="I19" s="10">
+        <f>SUM(I2:I18)</f>
         <v/>
       </c>
-      <c r="J18" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1780,7 +1841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3148,20 +3209,120 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
+          <t>Cyanobacterial screening platform for Rubisco mutant variants</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>10.1021/acssynbio.5c00065</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Seventh sweep (ACS, redone)</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>16 variants, under the floor -- the authors' own GitHub repository is named CbbM_16variants. Deep-sequenced competitive growth, so the shape is right and only the size is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Ultrahigh-throughput multiplexed screening from cell-free expression</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>10.1021/jacs.5c04962</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Seventh sweep (ACS, redone)</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>Not open access, no PMC record; a droplet-microfluidics methods paper rather than a variant dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Directed evolution of a genetically encoded chloride indicator</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>10.1021/acssynbio.4c00818</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Seventh sweep (ACS, redone)</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>fullTextXML empty; abstract describes a lineage to a named improved indicator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Stereoselective photoenzymatic hydroarylation</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>10.1021/jacs.5c12440</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Seventh sweep (ACS, redone)</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>fullTextXML empty; biocatalysis paper evolving to a named champion variant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
           <t>Affibody stability (DR5 / TNFR1)</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>10.1002/bit.28954</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t>Deep sequencing used only to triage candidates for individual validation; reported data is a handful of purified variants, not library-wide.</t>
         </is>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -10,9 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curated" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open (maybes)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partial rejections" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open (maybes)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Partial rejections'!$A$1:$H$38</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -44,7 +47,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +72,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -128,6 +136,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -495,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -544,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
@@ -554,7 +574,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>546125</v>
+        <v>546880</v>
       </c>
     </row>
     <row r="7">
@@ -587,391 +607,402 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Items excluded inside a curated paper (see 'Partial rejections')</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Source-organism category</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Datasets</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Variants</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Example proteins</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Bacteria</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>93677</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, creatinase</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Archaea</t>
+          <t>Bacteria</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1753</v>
+        <v>94126</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>ParLQ, PylRS (IFRS), pCNFRS, Tgo-D4K polymerase</t>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Yeast / fungi</t>
+          <t>Archaea</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>118603</v>
+        <v>1753</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>RNA Pol II Rpb1 (S. cerevisiae)</t>
+          <t>ParLQ, PylRS (IFRS), pCNFRS, Tgo-D4K polymerase</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Plants</t>
+          <t>Yeast / fungi</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>419</v>
+        <v>118603</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>AtHMT, CONSTANS (A. thaliana)</t>
+          <t>RNA Pol II Rpb1 (S. cerevisiae)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Viruses (incl. bacteriophage)</t>
+          <t>Plants</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>270545</v>
+        <v>725</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>TEV protease, influenza NEP, T7 RNA polymerase, Con1 (designed potyviral consensus)</t>
+          <t>AtHMT, CONSTANS (A. thaliana)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Viruses (incl. bacteriophage)</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>61070</v>
+        <v>270545</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>MET kinase domain, SHP2</t>
+          <t>TEV protease, influenza NEP, T7 RNA polymerase, Con1 (designed potyviral consensus)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>61070</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>MET kinase domain, SHP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Other (animal-derived)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C19" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>VHH nanobody, camelid-derived</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Subtotal: Prokaryotes (Bacteria + Archaea)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>91</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>95430</v>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Subtotal: Eukaryotes, non-human (Yeast/fungi + Plants + Other)</t>
+          <t xml:space="preserve">  Subtotal: Prokaryotes (Bacteria + Archaea)</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>119080</v>
+        <v>95879</v>
       </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B21" s="7">
-        <f>SUM(B12:B18)</f>
-        <v/>
-      </c>
-      <c r="C21" s="7">
-        <f>SUM(C12:C18)</f>
-        <v/>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Subtotal: Eukaryotes, non-human (Yeast/fungi + Plants + Other)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>119386</v>
       </c>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>SUM(B13:B19)</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>SUM(C13:C19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>'Papers' counts distinct DOIs within that category; a paper spanning several organisms (e.g. Jiang 2024/PRIME, which has datasets on a bacterium, an archaeon, a bacteriophage and a camelid nanobody) is counted once per category it touches, so the Papers column does not sum to the 17-paper total. Datasets and Variants do sum exactly to the Curated tab's totals -- every dataset has exactly one source_organism. 'Other (animal-derived)' is the VHH nanobody dataset, filed under datasets/ even though a camelid is not a bacterium, archaeon, yeast or plant -- the branch has no separate tree for it yet.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="24" ht="30" customHeight="1"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Sweep</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>What it searched</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Venue coverage</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>First sweep</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>"machine learning guided enzyme engineering" (+/- organism)</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>nature.com, 2025</t>
-        </is>
-      </c>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Second sweep</t>
+          <t>First sweep</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Same query, organism clause dropped</t>
+          <t>"machine learning guided enzyme engineering" (+/- organism)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Springer Nature via Europe PMC, 2025</t>
+          <t>nature.com, 2025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Third sweep</t>
+          <t>Second sweep</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>"deep mutational scanning" / "variant effect map" / "massively parallel mutagenesis" / "site-saturation mutagenesis"</t>
+          <t>Same query, organism clause dropped</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>All publishers via Europe PMC, 2025, open access</t>
+          <t>Springer Nature via Europe PMC, 2025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Fourth sweep (ACS) -- SUPERSEDED</t>
+          <t>Third sweep</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>No single boolean query recorded (unlike the other sweeps) -- browsed each journal's 2025 issue listings directly, then read title and abstract of anything protein/enzyme-shaped. Direct ACS access returns a 403 on articles and supplements, so retrieval went through Europe PMC. Redone systematically as the seventh sweep below, which found a paper this pass missed.</t>
+          <t>"deep mutational scanning" / "variant effect map" / "massively parallel mutagenesis" / "site-saturation mutagenesis"</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025, open access</t>
+          <t>All publishers via Europe PMC, 2025, open access</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Fifth sweep (PNAS)</t>
+          <t>Fourth sweep (ACS) -- SUPERSEDED</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Two separate matches, then deduped: title-matched on protein/enzyme-engineering terms (30 hits) and abstract-matched on landscape/library terms ("fitness landscape", "combinatorial library", etc., 11 hits) -- 41 unique papers total.</t>
+          <t>No single boolean query recorded (unlike the other sweeps) -- browsed each journal's 2025 issue listings directly, then read title and abstract of anything protein/enzyme-shaped. Direct ACS access returns a 403 on articles and supplements, so retrieval went through Europe PMC. Redone systematically as the seventh sweep below, which found a paper this pass missed.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>PNAS, 2025, open access</t>
+          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025, open access</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Sixth sweep (Cell Press)</t>
+          <t>Fifth sweep (PNAS)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Title-matched across the full journal family (43 hits) -- almost entirely clinical-ML iScience papers with no connection to protein engineering, so no separate abstract pass was run.</t>
+          <t>Two separate matches, then deduped: title-matched on protein/enzyme-engineering terms (30 hits) and abstract-matched on landscape/library terms ("fitness landscape", "combinatorial library", etc., 11 hits) -- 41 unique papers total.</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Cell, Mol Cell, Cell Chem Biol, Cell Systems, Structure, Cell Host &amp; Microbe, Immunity, Curr Biol, Chem, iScience, Cell Rep Methods, Cell Rep Phys Sci</t>
+          <t>PNAS, 2025, open access</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Seventh sweep (ACS, redone)</t>
+          <t>Sixth sweep (Cell Press)</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>The fourth sweep redone as a real query for parity with the others: JOURNAL:(5 ACS titles) AND PUB_YEAR:2025 AND SRC:MED AND (deep mutational scanning OR site-saturation mutagenesis OR directed evolution OR variant effect map OR massively parallel mutagenesis OR enzyme engineering OR protein engineering, as quoted phrases) -- 237 hits, 234 unseen; all 234 abstracts pulled and keyword-scored for per-variant-table signals. Found Somvilla 2025, which the manual pass had missed.</t>
+          <t>Title-matched across the full journal family (43 hits) -- almost entirely clinical-ML iScience papers with no connection to protein engineering, so no separate abstract pass was run.</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025</t>
+          <t>Cell, Mol Cell, Cell Chem Biol, Cell Systems, Structure, Cell Host &amp; Microbe, Immunity, Curr Biol, Chem, iScience, Cell Rep Methods, Cell Rep Phys Sci</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>Seventh sweep (ACS, redone)</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>The fourth sweep redone as a real query for parity with the others: JOURNAL:(5 ACS titles) AND PUB_YEAR:2025 AND SRC:MED AND (deep mutational scanning OR site-saturation mutagenesis OR directed evolution OR variant effect map OR massively parallel mutagenesis OR enzyme engineering OR protein engineering, as quoted phrases) -- 237 hits, 234 unseen; all 234 abstracts pulled and keyword-scored for per-variant-table signals. Found Somvilla 2025, which the manual pass had missed.</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>ACS Catal, ACS Cent Sci, ACS Synth Biol, JACS, Biochemistry, 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>Directed-evolution sweep</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>"directed evolution" / "site-saturation mutagenesis" / "laboratory evolution" / "yeast surface display"+"deep sequencing", explicitly excluding "deep mutational scanning" and "enzyme engineering" phrasing</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>All publishers via Europe PMC, 2025, journals only (no bioRxiv)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="34" ht="45" customHeight="1"/>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>See the 'Curated' tab for shipped datasets with variant counts, 'Rejected' for every paper chased to a documented reason, and 'Open (maybes)' for leads left for a future session. Full narrative detail, including access routes and per-sweep notes, is in candidates_2025.md on the 2025 branch.</t>
         </is>
@@ -979,9 +1010,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A35:E35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1313,14 +1344,14 @@
         </is>
       </c>
       <c r="H7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>176</v>
+        <v>931</v>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>AtHMT methyltransferase, substrate preference</t>
+          <t>AtHMT methyltransferase (482) and YmPhytase phytase (449); all four rounds of each autonomous engineering campaign, singles through quadruples</t>
         </is>
       </c>
     </row>
@@ -3339,6 +3370,1367 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="72" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Datasets shipped</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Item excluded</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Reason recorded in remark</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Audit verdict (2026-08-27)</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Follow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Zhang 2025 (IFRS, PylRS)</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-61952-2</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Catalytic efficiency kcat/Km(tRNA)</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Reported for too few variants</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Not re-verified</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Fig. 4b/4d/4f source sheets hold 5-15 rows each, consistent with the claim; not counted variant by variant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Zhang 2025 (IFRS, PylRS)</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-61952-2</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>ncAA panel of Fig. 3</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Measures separate parent synthetases rather than one wild type</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Zhang 2025 (IFRS, PylRS)</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-61952-2</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Myoglobin and multiple-amber constructs of Fig. 4</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Two or three variants each, under the 20-variant floor</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Huber 2025 (TEV protease)</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60622-7</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>TEVs substrate landscapes</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>The varying sequence is the seven-residue substrate motif, not the protease</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Huber 2025 (TEV protease)</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60622-7</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Panels of Fig. 1e, 3b, 4d, 4e</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Each covers fewer than twenty distinct protease genotypes</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed: 6, 12, 5 and 5 distinct protease genotypes; the row counts are protease x substrate combinations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Huber 2025 (TEV protease)</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60622-7</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Panel of Fig. 3a</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Grouped with the above as fewer than twenty distinct protease genotypes</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Imprecise</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Fig. 3a is 2 positions x 20 amino acids = 40 distinct genotypes, above the floor. Almost certainly redundant with the shipped library (positions 171 and 176); worth one check before acting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Duan 2025 (RNA Pol II)</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-63304-6</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>(none recorded)</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Landwehr 2025 (McbA)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-024-55399-0</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Four-site combinatorial training and test libraries on GitHub</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Measure a different library on the same enzyme</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>Wrong</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>Not a rejection reason -- a different library on the same enzyme is a separate dataset, which is exactly what this format curates. Verified live: data/ML_validation/*.xlsx and data/HSS/*.xlsx hold per-variant measured activity keyed by a four-letter code, 77-243 variants per file, across 9 substrates. All above the 20-variant floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Landwehr 2025 (McbA)</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-024-55399-0</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Zero-shot prediction tables</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Computed rather than assayed</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Landwehr 2025 (McbA)</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-024-55399-0</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Fig. 2b substrate scope</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Varies the reaction rather than the protein</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Yang 2025 (ALDE, ParLQ)</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-55987-8</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>trans-2a yield on its own</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>No higher-is-better orientation; the paper treats more trans product as worse</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Yang 2025 (ALDE, ParLQ)</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-55987-8</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Plate-normalized ALDE objective</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>A restatement of the same pair of yields</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Yang 2025 (ALDE, ParLQ)</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-55987-8</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Public benchmark landscapes used for simulation</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Belong to the publications that measured them</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Singh 2025 (AtHMT / YmPhytase)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-61209-y</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>The whole YmPhytase campaign</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>No sequence is given in the paper and no reference accession could be found, so its 180 round-one mutants cannot be placed on any sequence</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>Wrong</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-27. Supplementary Data 5 is titled "The DNA sequences for wild-type AtHMT and YmPhytase" in the Description of Additional Supplementary Files, and the Fig. 3 caption repeats the pointer. Its plasmid map gives a 434-aa ORF against which all 180 mutation labels verify at offset 0. Shipped as Singh 2025-ML-YmPhytase-catalyticactivity-relative_activity.csv, 181 variants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Singh 2025 (AtHMT / YmPhytase)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-61209-y</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>Rounds 2 to 4, both enzymes</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Built on several different improved parents per round with no per-well template assignment shipped, so a full genotype cannot be reconstructed</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>Wrong</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-27. The Mutations column of every round-2/3/4 sheet writes the full genotype ("V141M / K226G / I15V / Q295D"), so no template assignment is needed. Both datasets now pool all four rounds: AtHMT 176 -&gt; 482 variants, YmPhytase 181 -&gt; 449. The 482 reconciles exactly with the paper own Overview sheet total of 482 new mutants, and 449 is the stated 448 plus the T44V/K45E benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Zhang 2025 (PLMeAE, pCNF-RS)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-56751-8</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>UBC9 and ubiquitin benchmark landscapes</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Measured by other publications and belong to them</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Silverstein 2025 (PAMmla, SpCas9)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41586-025-09021-y</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>PAMmla predictions and the 64 million predicted profiles</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Computed rather than assayed</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Silverstein 2025 (PAMmla, SpCas9)</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41586-025-09021-y</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>GUIDE-seq2 results of Supplementary Table 6</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Measure off-target editing at genomic sites, not a fitness per enzyme variant</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Alamos 2025 (CONSTANS)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41587-025-02880-w</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>The 3,644 viral and 218 Arabidopsis tiles of Tables S1 and S2</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>Fragments of thousands of unrelated proteins rather than variants of one wild type</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Jiang 2024 (PRIME)</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.adr2641</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>(none recorded)</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Estevam 2025 (MET kinase)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>10.7554/eLife.101882</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>The exon-14-deleted MET background</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>A different construct, and would be its own set of datasets</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Wrong</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>OPEN -- a scope deferral written as a rejection. That it would be its own set of datasets is a reason to curate it, not to drop it; it would roughly double this paper yield to ~24 datasets. The eLife PMC package carries figures only and the data repository was not located in this audit, so availability is unconfirmed -- chase the Data availability statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Estevam 2025 (MET kinase)</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>10.7554/eLife.101882</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Machine-learning feature tables and predictions</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Computed rather than assayed</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Jiang 2025 (SHP2)</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60641-4</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Supplementary Data 3 Clinical Variants sheet</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>A cross-reference of the same enrichment data against ClinVar and COSMIC rather than an independent measurement</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Jiang 2025 (SHP2)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60641-4</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>COSMIC- and ClinVar-annotated sheets</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Carry no enrichment scores at all</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed: both sheets hold annotation columns only (tissue, histology, clinical significance, accession) and no score column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Jiang 2025 (SHP2)</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60641-4</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Molecular-dynamics and structural analyses</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Computational</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Wysocki 2025 (RbcL)</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>10.1021/acssynbio.5c00591</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Validation panel of the Supplementary Figure</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>A 1000-variant random sample of this same library, not an independent measurement</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Wysocki 2025 (RbcL)</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>10.1021/acssynbio.5c00591</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Synechococcus elongatus RbcL comparisons</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>No library-scale fitness table is given</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Not re-verified</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>Consistent with what is staged -- the supplementary workbook holds only SI Tables 1 and 2, both H. neapolitanus. Not checked against the SI PDF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Thornton 2025 (Con1 protease)</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>10.1021/acssynbio.5c00062</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Second, ML-guided round of 32 further variants (Figure 5)</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Per-region mutant index numbers are reused independently of the first-round indices, so merging by index would mix up genotypes</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>Well evidenced -- the remark names the concrete collision (region B mutant 27 vs the follow-up hit TB27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Thornton 2025 (Con1 protease)</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>10.1021/acssynbio.5c00062</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Purified-versus-CFPS comparison of Figure 6</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Validates a handful of variants rather than screening a library</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Teo 2025 (influenza NEP)</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>10.1016/j.celrep.2024.115196</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Influenza RNA species (mRNA/cRNA/vRNA) quantification</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>A separate assay on wild-type virus rather than a variant screen</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Wong 2025 (CjPglB)</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60526-6</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>The 328-construct PD Sequon Variant Sequences library (Fig. 6)</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>An insertion-site scan of a separate carrier protein rather than substitutions in CjPglB</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Wong 2025 (CjPglB)</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60526-6</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Seven-mutant Western blot validation panel</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Confirms a subset of the same screen rather than measuring independently</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Wong 2025 (CjPglB)</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-60526-6</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>RiPP recognition-element binding and lasso-peptide cyclization sections</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Characterize unrelated protein families</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Somvilla 2025 (SaAmd)</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c01903</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>FACS sorting data (Figures S7-S8)</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Population fluorescence distributions rather than per-variant scores</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Somvilla 2025 (SaAmd)</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c01903</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Library-composition tables (Table S2)</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>List what was randomized rather than what each variant did</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Somvilla 2025 (SaAmd)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c01903</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>PdAmd comparison (Figure S9)</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>A different enzyme rather than a variant of this wild type</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Singh 2025 (AtHMT / YmPhytase)</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-61209-y</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>AtHMT round-1 variant identity</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>Variant identity is not in the screening file, whose rows are plate wells; recovered by joining each well to the primer plate map of Supplementary Data 1</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>Wrong</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>Harmless but false -- the round-1 sheets carry their own Mutation column holding all 176 labels, identical to the set the primer-map join produced. The join was never needed. Corrected in the rebuilt remark 2026-08-27.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H38"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -80,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -102,11 +102,55 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -150,6 +194,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -554,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -564,7 +610,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>546880</v>
+        <v>575880</v>
       </c>
     </row>
     <row r="7">
@@ -584,7 +630,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -594,7 +640,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -604,7 +650,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -694,17 +740,17 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>118603</v>
+        <v>147603</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>RNA Pol II Rpb1 (S. cerevisiae)</t>
+          <t>RNA Pol II Rpb1 (S. cerevisiae), DAOx (Rhodotorula gracilis)</t>
         </is>
       </c>
     </row>
@@ -814,10 +860,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>119386</v>
+        <v>148386</v>
       </c>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -1000,9 +1046,36 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1"/>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Eighth sweep (2026)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>The first sweep of a year other than 2025, run 2026-09-04. Two Europe PMC queries: ABSTRACT:("deep mutational scanning" OR "site-saturation mutagenesis" OR "variant effect map") -- 66 hits; and ABSTRACT:("enzyme engineering" OR "protein engineering" OR "machine learning-guided") AND ABSTRACT:"variants" -- 45 hits. Both relevance-ordered and read to pageSize 40, so a top slice rather than an enumeration; the third, sixth and seventh sweeps are worth re-running verbatim against 2026.</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>All publishers via Europe PMC, 2026, open access, journals only</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Ninth sweep (display axis)</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="18" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>See the 'Curated' tab for shipped datasets with variant counts, 'Rejected' for every paper chased to a documented reason, and 'Open (maybes)' for leads left for a future session. Full narrative detail, including access routes and per-sweep notes, is in candidates_2025.md on the 2025 branch.</t>
         </is>
@@ -1024,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1840,26 +1913,78 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Vanella</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Nat Commun</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Decoding the substrate specificity landscape of a promiscuous enzyme through multi-substrate mutational scanning</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-69913-z</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>datasets</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>29000</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>D-amino acid oxidase (DAOx), Rhodotorula gracilis, 365 aa. One EP-Seq library of 5,800 single missense variants scored against five D-amino acid substrates, each at its Km -- one dataset per substrate. Readout is the source's expression-normalized activity fitness (WT = 1 by definition, no WT row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="10">
-        <f>SUM(H2:H18)</f>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="10">
+        <f>SUM(H2:H19)</f>
         <v/>
       </c>
-      <c r="I19" s="10">
-        <f>SUM(I2:I18)</f>
+      <c r="I20" s="10">
+        <f>SUM(I2:I19)</f>
         <v/>
       </c>
-      <c r="J19" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1872,7 +1997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3356,6 +3481,33 @@
       <c r="E59" s="11" t="inlineStr">
         <is>
           <t>Deep sequencing used only to triage candidates for individual validation; reported data is a handful of purified variants, not library-wide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Urease functional and catalytic landscape (H. pylori UreB)</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>10.1080/19490976.2026.2653575</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>Eighth sweep (2026)</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>58 alanine-scan point mutants clears the 20-variant floor, but the readouts are a spread of expression, growth, colonization and inhibitor-binding assays rather than one quantity measured across the panel, and the paper carries no data-availability statement at all. The separate 37-site phage-display library is not reported per variant.</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4775,8 +4927,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="n">
-        <v>1</v>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -4805,8 +4959,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n">
-        <v>2</v>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
@@ -4835,8 +4991,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
-        <v>3</v>
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
@@ -4861,6 +5019,70 @@
       <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Needs clone 97's parent CDR sequence from a different, earlier paper, and working out which numbered file per replicate is 'before' vs. 'after' selection -- not safe to guess at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Jansen 2026 -- CymR transcriptional repressor DMS (GROQ-Seq)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>10.1093/nar/gkag206</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Eighth sweep (2026)</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>CymR (TetR family, Pseudomonas putida, 202 aa), 7,887 variants over 24 conditions (+/- tetracycline x three ligands). Per-variant data is Supplementary file 1, a CSV, with Supplementary Table S3 as its column legend.</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Only the ~3,819 substitutions are curatable -- the ~4,040 insertions and ~201 deletions cannot be written as {WT}{position}{MUT}. Also needs a decision on which of the 24 conditions become datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Echinocandin resistance in S. cerevisiae -- Fks1 hotspot DMS</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>10.1093/genetics/iyag055</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Eighth sweep (2026)</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>465 single substitutions across three Fks1 hotspots, bulk-competition DMS with selection coefficients, against anidulafungin, caspofungin and micafungin plus a no-drug control -- four conditions on one WT.</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>No formal data-availability statement in the full text. The selection coefficients are presumably in the eleven supplementary tables, but that is a Phase 0 chase, not a decided fact.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -3852,12 +3852,12 @@
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>Wrong</t>
+          <t>SUPERSEDED 2026-09-05. The audit called this 'not a rejection reason' from the file listing alone. Opened: the nine *_train.xlsx files are 4-site single-mutant exports (4 x 19 + parent) whose sites all fall inside the shipped 64-residue screen and whose values match it 19/19 exactly -- ML training exports of data already curated, not a separate library. Only the two *_test.xlsx files hold new genotypes.</t>
         </is>
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>Not a rejection reason -- a different library on the same enzyme is a separate dataset, which is exactly what this format curates. Verified live: data/ML_validation/*.xlsx and data/HSS/*.xlsx hold per-variant measured activity keyed by a four-letter code, 77-243 variants per file, across 9 substrates. All above the 20-variant floor.</t>
+          <t>The new genotypes are 243 moclobemide and 169 metoclopramide multi-site variants, but the GitHub scale is unrecoverable (shipped/github ratio 1.2-15.8). Use Source Data 'Fig 4a' (moclobemide, 243 distinct) and 'Fig4b' (metoclopramide, 243, a superset), whose 'Actual' column is min-max normalized to the best variant = 1 -- a different denominator from the shipped fold-vs-WT, so two new datasets, not extra rows. Awaiting a decision.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>575880</v>
+        <v>576366</v>
       </c>
     </row>
     <row r="7">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>94126</v>
+        <v>94612</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
@@ -1329,14 +1329,14 @@
         </is>
       </c>
       <c r="H5" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>10909</v>
+        <v>11395</v>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>McbA amide synthetase; conversion of 9 pharmaceuticals</t>
+          <t>McbA amide synthetase; conversion of 9 pharmaceuticals Plus two ML-predicted combinatorial datasets (243 multi-site variants each, moclobemide and metoclopramide) from Source Data Fig 4a/4b, whose readout is normalized to the best variant in the set rather than to wild type.</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>The new genotypes are 243 moclobemide and 169 metoclopramide multi-site variants, but the GitHub scale is unrecoverable (shipped/github ratio 1.2-15.8). Use Source Data 'Fig 4a' (moclobemide, 243 distinct) and 'Fig4b' (metoclopramide, 243, a superset), whose 'Actual' column is min-max normalized to the best variant = 1 -- a different denominator from the shipped fold-vs-WT, so two new datasets, not extra rows. Awaiting a decision.</t>
+          <t>The new genotypes are 243 moclobemide and 169 metoclopramide multi-site variants, but the GitHub scale is unrecoverable (shipped/github ratio 1.2-15.8). Use Source Data 'Fig 4a' (moclobemide, 243 distinct) and 'Fig4b' (metoclopramide, 243, a superset), whose 'Actual' column is min-max normalized to the best variant = 1 -- a different denominator from the shipped fold-vs-WT, so two new datasets, not extra rows. SHIPPED 2026-09-05 as two datasets, 243 variants each, under Activity/CatalyticActivity/DMS/. The nine *_train.xlsx files remain not curatable.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>576366</v>
+        <v>605037</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -698,17 +698,17 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>94612</v>
+        <v>123283</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase</t>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, CymR</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1965,26 +1965,78 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Jansen</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Nucleic Acids Res</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Mapping the phenotypic landscape of a transcriptional repressor using deep mutational scanning and growth-based quantitative sequencing</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>10.1093/nar/gkag206</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>datasets</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>28671</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>CymR (TetR family, Pseudomonas putida), 203 aa, assayed as the S110G/A171V engineered parent. 9,557 substitution variants (singles through octuples) per dataset, one per ligand: perillic acid, perillyl alcohol, S-limonene. Readout is log10 fold induction Ginf/G0 from a Hill fit. First use of Activity/TranscriptionalRegulation/. The 11,671 insertion and deletion variants are out of format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="10">
-        <f>SUM(H2:H19)</f>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="10">
+        <f>SUM(H2:H20)</f>
         <v/>
       </c>
-      <c r="I20" s="10">
-        <f>SUM(I2:I19)</f>
+      <c r="I21" s="10">
+        <f>SUM(I2:I20)</f>
         <v/>
       </c>
-      <c r="J20" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4883,7 +4935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5030,12 +5082,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Jansen 2026 -- CymR transcriptional repressor DMS (GROQ-Seq)</t>
+          <t>Echinocandin resistance in S. cerevisiae -- Fks1 hotspot DMS</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10.1093/nar/gkag206</t>
+          <t>10.1093/genetics/iyag055</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -5045,42 +5097,10 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>CymR (TetR family, Pseudomonas putida, 202 aa), 7,887 variants over 24 conditions (+/- tetracycline x three ligands). Per-variant data is Supplementary file 1, a CSV, with Supplementary Table S3 as its column legend.</t>
+          <t>465 single substitutions across three Fks1 hotspots, bulk-competition DMS with selection coefficients, against anidulafungin, caspofungin and micafungin plus a no-drug control -- four conditions on one WT.</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Only the ~3,819 substitutions are curatable -- the ~4,040 insertions and ~201 deletions cannot be written as {WT}{position}{MUT}. Also needs a decision on which of the 24 conditions become datasets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Echinocandin resistance in S. cerevisiae -- Fks1 hotspot DMS</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>10.1093/genetics/iyag055</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Eighth sweep (2026)</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>465 single substitutions across three Fks1 hotspots, bulk-competition DMS with selection coefficients, against anidulafungin, caspofungin and micafungin plus a no-drug control -- four conditions on one WT.</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>No formal data-availability statement in the full text. The selection coefficients are presumably in the eleven supplementary tables, but that is a Phase 0 chase, not a decided fact.</t>
         </is>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -4935,7 +4935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5106,6 +5106,38 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Vanella 2024 -- the EP-Seq activity-stability paper behind Vanella 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-024-45630-3</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Eighth sweep (2026), found while curating Vanella 2026</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Same DAOx construct as the shipped Vanella 2026 datasets, so Phase 3 is already settled: 365 aa, P80324 1-365, confirmed from the plasmid at Zenodo 10.5281/zenodo.8388902. It is also the paper that actually measured the surface-display expression scores excluded from Vanella 2026, so curating it gives that data a legitimate home under its own authors. Activity-stability tradeoff framing suggests both an activity and a stability readout.</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Not chased yet. Its supplementary bundle and Zenodo deposit were downloaded during the Vanella 2026 work (record 8388902 includes a 2 GB PacBio FASTQ and a 14 GB Illumina zip -- filter by size). Needs Phase 0-1 from the top.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1074,8 +1074,26 @@
       <c r="D35" s="17" t="n"/>
       <c r="E35" s="18" t="n"/>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>The venues no journal-specific sweep had ever touched, 2025+2026, weighted to enzymes: an enzyme noun AND a library-scale method, per journal. 289 hits across 20 journals, all titles screened, 5 chased to data availability. Outcome: Science adu1058 rejected as a homolog panel (193 adenylate kinase orthologs at 42% mean identity), Protein Sci F1-ATPase rejected (data on request); open are Sci Adv aee9222 (15,000-variant form II rubisco, unreachable -- no PMC record), NAR gkag259 (T7 RNAP, table only in the SI PDF) and Protein Sci pro.70112 (myoglobin DMS, 2,577 rows on Zenodo, human tree). Verdict on the venues: the biotechnology journals (Biotechnol Bioeng, Synth Syst Biotechnol, Enzyme Microb Technol, Metab Eng -- 64 hits) yield nothing because their subject is pathway engineering, and Angew Chem's 62 hits are all one-champion biocatalysis.</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Nucleic Acids Res, Protein Sci, Chembiochem, Biotechnol Bioeng, Synth Syst Biotechnol, PEDS, Chem Sci, Science, Sci Adv, Nat Chem Biol, Nat Catal, AEM, Microb Biotechnol, Metab Eng, Angew Chem, Green Chem, Chem Commun, Biotechnol Biofuels, J Biotechnol, Enzyme Microb Technol -- 2025+2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>See the 'Curated' tab for shipped datasets with variant counts, 'Rejected' for every paper chased to a documented reason, and 'Open (maybes)' for leads left for a future session. Full narrative detail, including access routes and per-sweep notes, is in candidates_2025.md on the 2025 branch.</t>
         </is>
@@ -2049,7 +2067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3560,6 +3578,60 @@
       <c r="E60" s="11" t="inlineStr">
         <is>
           <t>58 alanine-scan point mutants clears the 20-variant floor, but the readouts are a spread of expression, growth, colonization and inhibitor-binding assays rather than one quantity measured across the panel, and the paper carries no data-availability statement at all. The separate 37-site phage-display library is not reported per variant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Evolutionary-scale enzymology of adenylate kinase</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>10.1126/science.adu1058</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>Homolog panel. kcat/KM measured by microfluidics for hundreds of ADK variants and all kinetics deposited at Zenodo 10.5281/zenodo.15022270, but the library is 193 orthologs of 42% mean pairwise identity; the only true mutants are LID-swap chimeras and a short cysteine series. No shared wild type, so no mutant column. Recorded because the abstract reads like the best enzyme dataset of the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>High-throughput mutational analysis of F1-ATPase</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>10.1002/pro.70699</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>Data availability is 'available from the corresponding author upon reasonable request', and the saturation covers only two residues (betaE190, betaY307).</t>
         </is>
       </c>
     </row>
@@ -4935,7 +5007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5138,6 +5210,102 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Form II rubisco fitness landscape (Gallionella sp.)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aee9222</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Best candidate of the tenth sweep. A barcoded library of 15,000 single-site and multi-site variants scored by growth-coupled selection in Synechocystis sp. PCC 6803 -- one wild type, bacterial, far above the floor, and a second rubisco to sit beside Wysocki's RbcL.</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Unreachable from here: Europe PMC has the record but inEPMC:'N', hasSuppl:'N', subscription only. Needs the article and its supplement dropped in by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>T7 RNA polymerase dual-fitness evolution</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>10.1093/nar/gkag259</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>T7 RNAP is already in the repo from Jiang 2024, so a second property on the same protein is worth having, and 'dual-fitness' means two readouts (Tm and high-temperature activity).</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>No deposited table -- data availability says 'All data described are contained within the article'. The supplemental zip holds three PDFs and no spreadsheet, but SI_NAR.pdf carries 249 distinct mutation labels with pages 25-29 dense in them. Needs PDF extraction per the Somvilla precedent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Thermostable myoglobin DMS (human)</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>10.1002/pro.70112</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Ready to curate: Zenodo 10658344 holds Figure_2_data.xlsx whose Figure_2A sheet is 2,577 per-variant rows with two replicate fitness columns and a cell count, and Figure_2B the mean with a missense/nonsense classification. Over 10,000 variants screened by yeast display, display level as a stability proxy.</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Nothing blocking it technically. Human myoglobin, so it lands in datasets_human/ and ranks below cellular non-human work.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>605037</v>
+        <v>607387</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -803,17 +803,17 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>61070</v>
+        <v>63420</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>MET kinase domain, SHP2</t>
+          <t>MET kinase domain, SHP2, myoglobin</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
@@ -1115,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2035,26 +2034,78 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Kung</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Protein Sci</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Deep mutational scanning reveals a de novo disulfide bond and combinatorial mutations for engineering thermostable myoglobin</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>10.1002/pro.70112</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>datasets_human</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Human myoglobin (hMb), 154 aa, identical to UniProt P02144. 2,350 missense variants covering all 154 positions, by yeast surface display and FACS. Readout is the expression fitness score (display level), which the paper validates as a thermostability proxy. First use of Expression/SurfaceDisplay/. Labels were renumbered by -136 off the Aga2p fusion construct. The 109 synonymous variants encode wild-type protein and collapse into the WT row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="10">
-        <f>SUM(H2:H20)</f>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="10">
+        <f>SUM(H2:H21)</f>
         <v/>
       </c>
-      <c r="I21" s="10">
-        <f>SUM(I2:I20)</f>
+      <c r="I22" s="10">
+        <f>SUM(I2:I21)</f>
         <v/>
       </c>
-      <c r="J21" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5007,7 +5058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5274,38 +5325,6 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Thermostable myoglobin DMS (human)</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>10.1002/pro.70112</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Tenth sweep (enzyme, never-swept journals)</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Ready to curate: Zenodo 10658344 holds Figure_2_data.xlsx whose Figure_2A sheet is 2,577 per-variant rows with two replicate fitness columns and a cell count, and Figure_2B the mean with a missense/nonsense classification. Over 10,000 variants screened by yeast display, display level as a stability proxy.</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Nothing blocking it technically. Human myoglobin, so it lands in datasets_human/ and ranks below cellular non-human work.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>607387</v>
+        <v>607715</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>270545</v>
+        <v>270873</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2086,26 +2086,78 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Jiang</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Nucleic Acids Res</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Deep learning-guided dual-fitness evolution of T7 RNA polymerase for enhanced stability and activity</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>10.1093/nar/gkag259</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>datasets_virus</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>T7 RNA polymerase, 883 aa, the same sequence already used by the Jiang 2024 datasets here. 164 multi-site variants (2 to 14 substitutions over 26 sites) with two readouts: Tm and transcriptional activity at 52 degC. Extracted from the SI PDF by word coordinates -- the paper deposits no machine-readable file -- by joining Table S3 (index to genotype) with Table S4 (index to readouts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="10">
-        <f>SUM(H2:H21)</f>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="10">
+        <f>SUM(H2:H22)</f>
         <v/>
       </c>
-      <c r="I22" s="10">
-        <f>SUM(I2:I21)</f>
+      <c r="I23" s="10">
+        <f>SUM(I2:I22)</f>
         <v/>
       </c>
-      <c r="J22" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5058,7 +5110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5293,38 +5345,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>T7 RNA polymerase dual-fitness evolution</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>10.1093/nar/gkag259</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Tenth sweep (enzyme, never-swept journals)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>T7 RNAP is already in the repo from Jiang 2024, so a second property on the same protein is worth having, and 'dual-fitness' means two readouts (Tm and high-temperature activity).</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>No deposited table -- data availability says 'All data described are contained within the article'. The supplemental zip holds three PDFs and no spreadsheet, but SI_NAR.pdf carries 249 distinct mutation labels with pages 25-29 dense in them. Needs PDF extraction per the Somvilla precedent.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>607715</v>
+        <v>576694</v>
       </c>
     </row>
     <row r="7">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -698,17 +698,17 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>123283</v>
+        <v>94612</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, CymR</t>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase</t>
         </is>
       </c>
     </row>
@@ -803,17 +803,17 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>63420</v>
+        <v>61070</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>MET kinase domain, SHP2, myoglobin</t>
+          <t>MET kinase domain, SHP2</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1182,8 +1182,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
-        <v>1</v>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
@@ -1226,8 +1228,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
-        <v>2</v>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
@@ -1270,8 +1274,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>3</v>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
@@ -1314,8 +1320,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
@@ -1358,8 +1366,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -1402,8 +1412,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
@@ -1446,8 +1458,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -1490,8 +1504,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
@@ -1534,8 +1550,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>9</v>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -1578,8 +1596,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>10</v>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
@@ -1622,8 +1642,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>11</v>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -1666,8 +1688,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>12</v>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
@@ -1710,8 +1734,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
-        <v>13</v>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -1754,8 +1780,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
-        <v>14</v>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
@@ -1798,8 +1826,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>15</v>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -1842,8 +1872,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
-        <v>16</v>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
@@ -1886,8 +1918,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
-        <v>17</v>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1989,7 +2023,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Jansen</t>
+          <t>Jiang</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -2004,160 +2038,56 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Mapping the phenotypic landscape of a transcriptional repressor using deep mutational scanning and growth-based quantitative sequencing</t>
+          <t>Deep learning-guided dual-fitness evolution of T7 RNA polymerase for enhanced stability and activity</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>10.1093/nar/gkag206</t>
+          <t>10.1093/nar/gkag259</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>datasets</t>
+          <t>datasets_virus</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>28671</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>CymR (TetR family, Pseudomonas putida), 203 aa, assayed as the S110G/A171V engineered parent. 9,557 substitution variants (singles through octuples) per dataset, one per ligand: perillic acid, perillyl alcohol, S-limonene. Readout is log10 fold induction Ginf/G0 from a Hill fit. First use of Activity/TranscriptionalRegulation/. The 11,671 insertion and deletion variants are out of format.</t>
+          <t>T7 RNA polymerase, 883 aa, the same sequence already used by the Jiang 2024 datasets here. 164 multi-site variants (2 to 14 substitutions over 26 sites) with two readouts: Tm and transcriptional activity at 52 degC. Extracted from the SI PDF by word coordinates -- the paper deposits no machine-readable file -- by joining Table S3 (index to genotype) with Table S4 (index to readouts).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Kung</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Protein Sci</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Deep mutational scanning reveals a de novo disulfide bond and combinatorial mutations for engineering thermostable myoglobin</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>10.1002/pro.70112</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>datasets_human</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Human myoglobin (hMb), 154 aa, identical to UniProt P02144. 2,350 missense variants covering all 154 positions, by yeast surface display and FACS. Readout is the expression fitness score (display level), which the paper validates as a thermostability proxy. First use of Expression/SurfaceDisplay/. Labels were renumbered by -136 off the Aga2p fusion construct. The 109 synonymous variants encode wild-type protein and collapse into the WT row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Jiang</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Nucleic Acids Res</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Deep learning-guided dual-fitness evolution of T7 RNA polymerase for enhanced stability and activity</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>10.1093/nar/gkag259</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>datasets_virus</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>T7 RNA polymerase, 883 aa, the same sequence already used by the Jiang 2024 datasets here. 164 multi-site variants (2 to 14 substitutions over 26 sites) with two readouts: Tm and transcriptional activity at 52 degC. Extracted from the SI PDF by word coordinates -- the paper deposits no machine-readable file -- by joining Table S3 (index to genotype) with Table S4 (index to readouts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="10">
-        <f>SUM(H2:H22)</f>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="10">
+        <f>SUM(H2:H20)</f>
         <v/>
       </c>
-      <c r="I23" s="10">
-        <f>SUM(I2:I22)</f>
+      <c r="I21" s="10">
+        <f>SUM(I2:I20)</f>
         <v/>
       </c>
-      <c r="J23" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2170,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3735,6 +3665,60 @@
       <c r="E62" s="11" t="inlineStr">
         <is>
           <t>Data availability is 'available from the corresponding author upon reasonable request', and the saturation covers only two residues (betaE190, betaY307).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Jansen 2026, CymR transcriptional repressor DMS</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>10.1093/nar/gkag206</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Out of the enzyme scope set on 2026-08-31. CymR is a TetR-family transcriptional repressor: a DNA-binding regulatory protein, not a catalyst and not catalytic machinery. Curated on this branch in error (3 datasets, 9,557 variants each, log10 fold induction across three ligands) and reverted once the scope was found on the 2022 and 2023 branches, where it had never been propagated to 2025. The data itself is sound and the extraction verified against the source's own mutation_codes column, so this is a scope rejection, not a quality one -- worth revisiting if the scope ever widens to regulatory proteins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Kung 2025, human myoglobin surface-display DMS</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>10.1002/pro.70112</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>Out of the enzyme scope set on 2026-08-31. Myoglobin is an oxygen-binding heme protein, not a catalyst, and the readout is yeast surface display level, which reports folding and abundance rather than catalysis -- the same reasoning the scope note applies to GFP, whose fluorescence 'reports chromophore maturation and folding rather than catalysis'. Curated in error (1 dataset, 2,350 variants, all 154 positions) and reverted. Data quality was not the issue: the sequence matched P02144 exactly and the paper's own nonsense and synonymous statistics re-derived.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>576694</v>
+        <v>594214</v>
       </c>
     </row>
     <row r="7">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -698,17 +698,17 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>94612</v>
+        <v>112132</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase</t>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, rubisco (R. rubrum)</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2068,26 +2068,78 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Prywes</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>A map of the rubisco biochemical landscape</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>10.1038/s41586-024-08455-0</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>datasets</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>17520</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Rubisco large subunit (Form II) from Rhodospirillum rubrum, 466 aa, matching NCBI WP_011390153.1 exactly. 8,760 single amino acid substitutions -- 99% of all possible -- scored by a growth-coupled selection in engineered E. coli. Two readouts: carboxylation fitness and relative Vmax, both normalized to wild type = 1. The apparent CO2 affinity K_C is left open, needing its own directory and a quality filter. Note the DOI reads s41586-024 but the version of record is Nature 638 (2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="10">
-        <f>SUM(H2:H20)</f>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="10">
+        <f>SUM(H2:H21)</f>
         <v/>
       </c>
-      <c r="I21" s="10">
-        <f>SUM(I2:I20)</f>
+      <c r="I22" s="10">
+        <f>SUM(I2:I21)</f>
         <v/>
       </c>
-      <c r="J21" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2100,7 +2152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3719,6 +3771,33 @@
       <c r="E64" s="11" t="inlineStr">
         <is>
           <t>Out of the enzyme scope set on 2026-08-31. Myoglobin is an oxygen-binding heme protein, not a catalyst, and the readout is yeast surface display level, which reports folding and abundance rather than catalysis -- the same reasoning the scope note applies to GFP, whose fluorescence 'reports chromophore maturation and folding rather than catalysis'. Curated in error (1 dataset, 2,350 variants, all 154 positions) and reverted. Data quality was not the issue: the sequence matched P02144 exactly and the paper's own nonsense and synonymous statistics re-derived.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Yeast-display A-beta-fibril conformational antibody campaign</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>10.3389/fimmu.2025.1655893</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Directed-evolution sweep</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>Retired from the open list on 2026-09-07 when the enzyme scope was propagated to this branch: an antibody is a binding domain, which the scope excludes, so the NGS parsing problem that was blocking it no longer matters.</t>
         </is>
       </c>
     </row>
@@ -5209,27 +5288,27 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Yeast-display A-beta-fibril conformational antibody campaign</t>
+          <t>Echinocandin resistance in S. cerevisiae -- Fks1 hotspot DMS</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>10.3389/fimmu.2025.1655893</t>
+          <t>10.1093/genetics/iyag055</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Directed-evolution sweep</t>
+          <t>Eighth sweep (2026)</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Real NGS sort-round data deposited on GitHub (Tessier-Lab-UMich/druglike-abeta-antibodies): CDR-sequence frequency tables for a defined 10-site NNK library (5 in HCDR1, 5 in LCDR2) built off a named parent antibody ('clone 97').</t>
+          <t>465 single substitutions across three Fks1 hotspots, bulk-competition DMS with selection coefficients, against anidulafungin, caspofungin and micafungin plus a no-drug control -- four conditions on one WT.</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Needs clone 97's parent CDR sequence from a different, earlier paper, and working out which numbered file per replicate is 'before' vs. 'after' selection -- not safe to guess at.</t>
+          <t>No formal data-availability statement in the full text. The selection coefficients are presumably in the eleven supplementary tables, but that is a Phase 0 chase, not a decided fact.</t>
         </is>
       </c>
     </row>
@@ -5241,27 +5320,27 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Echinocandin resistance in S. cerevisiae -- Fks1 hotspot DMS</t>
+          <t>Vanella 2024 -- the EP-Seq activity-stability paper behind Vanella 2026</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10.1093/genetics/iyag055</t>
+          <t>10.1038/s41467-024-45630-3</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Eighth sweep (2026)</t>
+          <t>Eighth sweep (2026), found while curating Vanella 2026</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>465 single substitutions across three Fks1 hotspots, bulk-competition DMS with selection coefficients, against anidulafungin, caspofungin and micafungin plus a no-drug control -- four conditions on one WT.</t>
+          <t>Same DAOx construct as the shipped Vanella 2026 datasets, so Phase 3 is already settled: 365 aa, P80324 1-365, confirmed from the plasmid at Zenodo 10.5281/zenodo.8388902. It is also the paper that actually measured the surface-display expression scores excluded from Vanella 2026, so curating it gives that data a legitimate home under its own authors. Activity-stability tradeoff framing suggests both an activity and a stability readout.</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>No formal data-availability statement in the full text. The selection coefficients are presumably in the eleven supplementary tables, but that is a Phase 0 chase, not a decided fact.</t>
+          <t>Not chased yet. Its supplementary bundle and Zenodo deposit were downloaded during the Vanella 2026 work (record 8388902 includes a 2 GB PacBio FASTQ and a 14 GB Illumina zip -- filter by size). Needs Phase 0-1 from the top.</t>
         </is>
       </c>
     </row>
@@ -5273,27 +5352,27 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Vanella 2024 -- the EP-Seq activity-stability paper behind Vanella 2026</t>
+          <t>Form II rubisco fitness landscape (Gallionella sp.)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>10.1038/s41467-024-45630-3</t>
+          <t>10.1126/sciadv.aee9222</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Eighth sweep (2026), found while curating Vanella 2026</t>
+          <t>Tenth sweep (enzyme, never-swept journals)</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Same DAOx construct as the shipped Vanella 2026 datasets, so Phase 3 is already settled: 365 aa, P80324 1-365, confirmed from the plasmid at Zenodo 10.5281/zenodo.8388902. It is also the paper that actually measured the surface-display expression scores excluded from Vanella 2026, so curating it gives that data a legitimate home under its own authors. Activity-stability tradeoff framing suggests both an activity and a stability readout.</t>
+          <t>Best candidate of the tenth sweep. A barcoded library of 15,000 single-site and multi-site variants scored by growth-coupled selection in Synechocystis sp. PCC 6803 -- one wild type, bacterial, far above the floor, and a second rubisco to sit beside Wysocki's RbcL.</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Not chased yet. Its supplementary bundle and Zenodo deposit were downloaded during the Vanella 2026 work (record 8388902 includes a 2 GB PacBio FASTQ and a 14 GB Illumina zip -- filter by size). Needs Phase 0-1 from the top.</t>
+          <t>Unreachable from here: Europe PMC has the record but inEPMC:'N', hasSuppl:'N', subscription only. Needs the article and its supplement dropped in by hand.</t>
         </is>
       </c>
     </row>
@@ -5305,27 +5384,27 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Form II rubisco fitness landscape (Gallionella sp.)</t>
+          <t>Prywes 2025 rubisco -- the apparent CO2 affinity K_C</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aee9222</t>
+          <t>10.1038/s41586-024-08455-0</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Tenth sweep (enzyme, never-swept journals)</t>
+          <t>Tenth/eleventh sweep</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Best candidate of the tenth sweep. A barcoded library of 15,000 single-site and multi-site variants scored by growth-coupled selection in Synechocystis sp. PCC 6803 -- one wild type, bacterial, far above the floor, and a second rubisco to sit beside Wysocki's RbcL.</t>
+          <t>The third readout of a paper already curated here for fitness and Vmax. K_C is the quantity the paper is really about, and a genuinely different measurement from velocity. Decisions already taken: it goes to a new Activity/SubstrateAffinity/, expressed as 1/K_C in mM^-1 so higher is better, from the Km_median column of Supplementary Data 2.</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Unreachable from here: Europe PMC has the record but inEPMC:'N', hasSuppl:'N', subscription only. Needs the article and its supplement dropped in by hand.</t>
+          <t>Needs the quality filter applied, not the raw column: the paper estimates K_C for only 65% of variants, and Km_qbcov &lt;= 1.0 reproduces its stated 5,687 exactly (5,686 mutants + WT) on the GitHub deposit, giving 5,667 on the publisher's supplement. Shipping unfiltered would pass every validator and be wrong.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>594214</v>
+        <v>599881</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>112132</v>
+        <v>117799</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>8</v>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Rubisco large subunit (Form II) from Rhodospirillum rubrum, 466 aa, matching NCBI WP_011390153.1 exactly. 8,760 single amino acid substitutions -- 99% of all possible -- scored by a growth-coupled selection in engineered E. coli. Two readouts: carboxylation fitness and relative Vmax, both normalized to wild type = 1. The apparent CO2 affinity K_C is left open, needing its own directory and a quality filter. Note the DOI reads s41586-024 but the version of record is Nature 638 (2025).</t>
+          <t>Rubisco large subunit (Form II) from Rhodospirillum rubrum, 466 aa, matching NCBI WP_011390153.1 exactly. 8,760 single amino acid substitutions -- 99% of all possible -- scored by a growth-coupled selection in engineered E. coli. Three readouts: carboxylation fitness and relative Vmax, both normalized to wild type = 1, in Activity/CatalyticActivity/; and the apparent CO2 affinity as 1/K_C in mM^-1 in a new Activity/SubstrateAffinity/, filtered to the 5,667 variants whose bootstrap coefficient of variation is under 1, the cut the paper itself applies. Note the DOI reads s41586-024 but the version of record is Nature 638 (2025).</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5376,38 +5376,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Prywes 2025 rubisco -- the apparent CO2 affinity K_C</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>10.1038/s41586-024-08455-0</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Tenth/eleventh sweep</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>The third readout of a paper already curated here for fitness and Vmax. K_C is the quantity the paper is really about, and a genuinely different measurement from velocity. Decisions already taken: it goes to a new Activity/SubstrateAffinity/, expressed as 1/K_C in mM^-1 so higher is better, from the Km_median column of Supplementary Data 2.</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Needs the quality filter applied, not the raw column: the paper estimates K_C for only 65% of variants, and Km_qbcov &lt;= 1.0 reproduces its stated 5,687 exactly (5,686 mutants + WT) on the GitHub deposit, giving 5,667 on the publisher's supplement. Shipping unfiltered would pass every validator and be wrong.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partial rejections" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open (maybes)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parked (other years)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Partial rejections'!$A$1:$H$38</definedName>
@@ -47,7 +48,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F6228"/>
       </patternFill>
     </fill>
   </fills>
@@ -150,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -196,6 +202,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -640,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5173,7 +5182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5280,99 +5289,153 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="110" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Paper (short label)</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>Publication year</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>Journal / record</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>Where it belongs, and what is already known</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="120" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Vanella 2024 -- the EP-Seq activity-stability paper behind Vanella 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-024-45630-3</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Nat Commun 2024</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Fully reachable (PMC10902396, open access, supplement present). Phase 3 is already settled from the Vanella 2026 work: DAOx, 365 aa, P80324 1-365, confirmed against the plasmid at Zenodo 10.5281/zenodo.8388902 -- whose record also holds a 2 GB PacBio FASTQ and a 14 GB Illumina zip, so filter the files array by size before downloading. It is the paper that measured the surface-display expression scores excluded from Vanella 2026, so curating it gives that data a home under its own authors. Belongs on the 2024 branch, which exists at origin/2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Echinocandin resistance in S. cerevisiae -- Fks1 hotspot DMS</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>10.1093/genetics/iyag055</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Genetics 2026</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>The Open tab recorded this as a data-availability chase; that note is stale. The record is PMC13147539, inEPMC:Y, isOpenAccess:Y, hasSuppl:Y -- full text and supplement both fetch cleanly. 465 single substitutions across three Fks1 hotspots, bulk-competition DMS with selection coefficients against anidulafungin, caspofungin and micafungin plus a no-drug control: four conditions on one wild type, comfortably above the floor and in scope. The only thing wrong with it is the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Echinocandin resistance in S. cerevisiae -- Fks1 hotspot DMS</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>10.1093/genetics/iyag055</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Eighth sweep (2026)</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>465 single substitutions across three Fks1 hotspots, bulk-competition DMS with selection coefficients, against anidulafungin, caspofungin and micafungin plus a no-drug control -- four conditions on one WT.</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>No formal data-availability statement in the full text. The selection coefficients are presumably in the eleven supplementary tables, but that is a Phase 0 chase, not a decided fact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Vanella 2024 -- the EP-Seq activity-stability paper behind Vanella 2026</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>10.1038/s41467-024-45630-3</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Eighth sweep (2026), found while curating Vanella 2026</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Same DAOx construct as the shipped Vanella 2026 datasets, so Phase 3 is already settled: 365 aa, P80324 1-365, confirmed from the plasmid at Zenodo 10.5281/zenodo.8388902. It is also the paper that actually measured the surface-display expression scores excluded from Vanella 2026, so curating it gives that data a legitimate home under its own authors. Activity-stability tradeoff framing suggests both an activity and a stability readout.</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Not chased yet. Its supplementary bundle and Zenodo deposit were downloaded during the Vanella 2026 work (record 8388902 includes a 2 GB PacBio FASTQ and a 14 GB Illumina zip -- filter by size). Needs Phase 0-1 from the top.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Form II rubisco fitness landscape (Gallionella sp.)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>10.1126/sciadv.aee9222</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Tenth sweep (enzyme, never-swept journals)</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Best candidate of the tenth sweep. A barcoded library of 15,000 single-site and multi-site variants scored by growth-coupled selection in Synechocystis sp. PCC 6803 -- one wild type, bacterial, far above the floor, and a second rubisco to sit beside Wysocki's RbcL.</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Unreachable from here: Europe PMC has the record but inEPMC:'N', hasSuppl:'N', subscription only. Needs the article and its supplement dropped in by hand.</t>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Science Advances 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Recorded here as needing the article dropped in by hand, but the year makes that moot: Europe PMC gives pubYear 2026 (pmid 42696565), inEPMC:N, hasSuppl:N, subscription only. A barcoded library of 15,000 single- and multi-site variants of a Gallionella Form II rubisco scored by growth-coupled selection in Synechocystis sp. PCC 6803 -- a strong candidate, and a second rubisco to sit beside Prywes and Wysocki, but for a 2026 branch and with the paywall still to solve.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2161,7 +2161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3807,6 +3807,33 @@
       <c r="E65" s="11" t="inlineStr">
         <is>
           <t>Retired from the open list on 2026-09-07 when the enzyme scope was propagated to this branch: an antibody is a binding domain, which the scope excludes, so the NGS parsing problem that was blocking it no longer matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Class A beta-lactamase gatekeeper-residue screen (BlaC, CTX-M-14, KPC-2, NmcA, TEM-1)</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>10.1016/j.jbc.2025.110347</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Directed-evolution sweep</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>Worked up in full on 2026-09-07 and rejected on shape, not on data quality. Supplementary Data 2 (mmc2.xls) is genuine deep-sequencing data -- five sheets, one per enzyme, each with seven condition blocks (ampicillin, carbenicillin, meropenem, ceftriaxone, clavulanic acid, sulbactam, avibactam) in three replicates, carrying raw unselected and selected counts, averaged relative fitness, errors and significance calls. But every block saturates the same single position, Ambler 105, so it would become 35 datasets of 15-19 substitutions each, 651 variant rows in total, mean 18.6, none reaching this branch's 20-variant floor: BlaC 19/17/19/19/19/19/19, CTX-M-14 19 x7, KPC-2 16/17/19/19/19/16/15, NmcA 19 x7, TEM-1 19 x7 (the shortfalls are real -- fitness is undefined where the selected count is zero). Three reasons beyond the count. A one-position scan is a 20-way ranking at one site rather than a fitness landscape, and the sequence column would make it indistinguishable from a real DMS. 35 files would be 22% of the repository's dataset count for 0.11% of its variants, distorting every per-dataset figure in the Summary tab. And Ambler 105 is a structural-alignment number rather than a sequence index, so Phase 3 would be five separate alignments, each an opportunity to place the substitution on the wrong residue. Revisit only if the floor is ever redefined as 'genuine deep-sequencing data' rather than library-scale coverage.</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5233,12 +5260,12 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>Class A beta-lactamase gatekeeper-residue screen (5 enzymes)</t>
+          <t>Tryptophan decarboxylase (TDC) active-site recombination (SUMS)</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>10.1016/j.jbc.2025.110347</t>
+          <t>10.1002/pro.70356</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
@@ -5248,42 +5275,10 @@
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>Genuine deep-sequencing fitness data in a legacy .xls (needs xlrd): site saturation of Ambler position 105 in BlaC, CTX-M-14, KPC-2, NmcA, TEM-1, each vs. 7 substrates/inhibitors, 3 replicates, raw counts and per-replicate fitness values -- not just a figure.</t>
+          <t>Substrate-multiplexed screening across 5 active-site positions; a clean prior single-site-saturation sub-library (96 unique single mutants) plus iterative combinatorial recombination libraries (~250 variants total, up to triple mutants, LC-MS-quantified). Multi-site labels are within format scope.</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>Single saturated position per enzyme: 19 substitutions + WT, one row under this branch's usual floor. Worth a second look if the bar is 'genuine deep-sequencing data' rather than 'library-scale'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Tryptophan decarboxylase (TDC) active-site recombination (SUMS)</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>10.1002/pro.70356</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Directed-evolution sweep</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>Substrate-multiplexed screening across 5 active-site positions; a clean prior single-site-saturation sub-library (96 unique single mutants) plus iterative combinatorial recombination libraries (~250 variants total, up to triple mutants, LC-MS-quantified). Multi-site labels are within format scope.</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Data availability is 'upon reasonable request' -- nothing machine-readable found in the supplement. Needs an email to the authors.</t>
         </is>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>599881</v>
+        <v>600043</v>
       </c>
     </row>
     <row r="7">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -707,17 +707,17 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>117799</v>
+        <v>117961</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, rubisco (R. rubrum)</t>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, rubisco (R. rubrum), tryptophan decarboxylase (R. gnavus)</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2129,26 +2129,78 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>McDonald</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Protein Science</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Active site diversification of a non-canonical amino acid decarboxylase by merging substrate multiplexed screening with computationally guided recombination</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>10.1002/pro.70356</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>datasets</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>Tryptophan decarboxylase from Ruminococcus gnavus, the 498-aa C-His construct printed in the supplement, whose first 490 residues are UniProt A7B1V0 exactly. A curated 27-variant panel recombining six active-site positions (F98, V99, L339, I343, W349, L355), 2-5 substitutions each, assayed by UPLC-MS against twelve tryptophan analogues. Six substrate columns shipped, six dropped where the one-decimal fold activities did not resolve 27 variants. Built from Supplementary Tables 2 and 3 read together and extracted from the PDF by word coordinates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="10">
-        <f>SUM(H2:H21)</f>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="10">
+        <f>SUM(H2:H22)</f>
         <v/>
       </c>
-      <c r="I22" s="10">
-        <f>SUM(I2:I21)</f>
+      <c r="I23" s="10">
+        <f>SUM(I2:I22)</f>
         <v/>
       </c>
-      <c r="J22" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5209,7 +5261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5249,38 +5301,6 @@
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>What's blocking it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>Tryptophan decarboxylase (TDC) active-site recombination (SUMS)</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>10.1002/pro.70356</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Directed-evolution sweep</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>Substrate-multiplexed screening across 5 active-site positions; a clean prior single-site-saturation sub-library (96 unique single mutants) plus iterative combinatorial recombination libraries (~250 variants total, up to triple mutants, LC-MS-quantified). Multi-site labels are within format scope.</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>Data availability is 'upon reasonable request' -- nothing machine-readable found in the supplement. Needs an email to the authors.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5261,7 +5261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5301,6 +5301,102 @@
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>What's blocking it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Nuclease activity landscape, 55,000 variants (TeleProt)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>10.1016/j.cels.2025.101236</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Twelfth sweep (OA filter removed)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>The abstract states the authors 'released a dataset of 55,000 nuclease variants, one of the most extensive genotype-phenotype enzyme activity landscapes to date'. A nuclease is in the enzyme scope, the readout is catalytic activity, and 55,000 would be among the largest datasets in this repository. Cell Systems 2025, Google Research; a bioRxiv preprint exists at 10.1101/2024.03.21.585615.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS THE USER. The paper is CC-BY per Crossref and Unpaywall (oa_status hybrid), so it is free -- but cell.com returns 403 to any automated fetch, and so does biorxiv.org. Please download the article PDF and its supplementary/STAR Methods from https://www.cell.com/cell-systems/pdf/S2405-4712(25)00069-9.pdf and drop them in. The data availability statement is what is actually needed: it should name where the 55,000 variants live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Multi-environment DMS of a bacterial kinase across temperatures</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>10.1016/j.celrep.2025.116446</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Twelfth sweep (OA filter removed)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>A genuine deep mutational scan of an enzyme performed at multiple temperatures -- several conditions on one wild type, so several datasets -- identifying temperature-sensitive and temperature-resistant substitutions. The paper's own argument is that single-condition landscapes hide condition-dependent effects, which is exactly the axis this benchmark is thin on. Cell Reports 2025.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS THE USER. Unpaywall reports oa_status gold with a direct PDF at https://www.cell.com/cell-reports/pdf/S2211-1247(25)01217-3.pdf, but cell.com returns 403 to automated fetches. Please download that PDF and the supplementary files. No preprint exists. Note Europe PMC records this as OPEN_ACCESS:N, inEPMC:N -- that flag is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TEV protease engineered by enzyme-substrate co-display on yeast</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>10.1093/protein/gzaf011</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Twelfth sweep (OA filter removed)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Yeast surface display co-presenting protease mutants with their substrate, so activity is read by loss of an epitope tag under flow cytometry. A protease is in scope and the method is library-scale on its face.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>No action needed yet. PMC13010152 is already assigned but live:False -- it is under embargo and will become fetchable on its own. Re-check rather than chase.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>600043</v>
+        <v>602323</v>
       </c>
     </row>
     <row r="7">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -707,17 +707,17 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>117961</v>
+        <v>120241</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, rubisco (R. rubrum), tryptophan decarboxylase (R. gnavus)</t>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, rubisco (R. rubrum), tryptophan decarboxylase (R. gnavus), EnvZ histidine kinase (E. coli)</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2181,26 +2181,78 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Ghose</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Cell Reports</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Multi-environment deep mutational scanning reveals the distribution of temperature-sensitive variants in a bacterial kinase</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>10.1016/j.celrep.2025.116446</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>datasets</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>EnvZ, the E. coli osmosensing histidine kinase, UniProt P0AEJ4, 450 aa. Single-site saturation of the DHp domain (positions 230-289, located by exact string match against the 60-aa MaveDB target). 1,140 substitutions per temperature, read out as GFP expression downstream of the cognate regulator OmpR. Curated from the authors' MaveDB deposit (urn:mavedb:00001240-a, CC0), not the article, which is CC-BY but which cell.com will not serve to an automated fetch. Two of the three temperature arms shipped: the 37 C arm was dropped because its nonsense variants score higher than wild type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="10">
-        <f>SUM(H2:H22)</f>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="10">
+        <f>SUM(H2:H23)</f>
         <v/>
       </c>
-      <c r="I23" s="10">
-        <f>SUM(I2:I22)</f>
+      <c r="I24" s="10">
+        <f>SUM(I2:I23)</f>
         <v/>
       </c>
-      <c r="J23" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3900,7 +3952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5249,6 +5301,48 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Ghose 2025 (EnvZ multi-environment DMS)</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>10.1016/j.celrep.2025.116446</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>The 37 C arm, urn:mavedb:00001240-a-3, 1,122 substitutions</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>Fails the experiment's own internal control. The 59 nonsense variants truncate the kinase and must be dead; at 30 C and 42 C their median score is 2.26 and 2.15 against a wild type of 3.73, but at 37 C it is 3.754 against a wild type of 3.639 -- a truncated EnvZ scoring higher than the intact one. 556 of 1,122 substitutions (50%) fall on the dead side of that median. fold_induction does not rescue it: it separates WT (73.3) from nonsense (1.18) but puts the median substitution at 1.16, which would make nearly every mutation lethal at 37 C and contradict the paper's own finding of high mutational tolerance. The 37 C file is also the only one of the three at full float precision rather than 2 dp, so it looks differently processed.</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>n/a -- found on curation 2026-09-07, not by the 2026-08-27 audit</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>Revisit if the article's methods become available; cell.com blocks automated retrieval of the CC-BY PDF, so the paper's own treatment of the 37 C arm is unread. Would have passed every validator in this repository.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5261,7 +5355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5344,12 +5438,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Multi-environment DMS of a bacterial kinase across temperatures</t>
+          <t>TEV protease engineered by enzyme-substrate co-display on yeast</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.celrep.2025.116446</t>
+          <t>10.1093/protein/gzaf011</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -5359,42 +5453,10 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>A genuine deep mutational scan of an enzyme performed at multiple temperatures -- several conditions on one wild type, so several datasets -- identifying temperature-sensitive and temperature-resistant substitutions. The paper's own argument is that single-condition landscapes hide condition-dependent effects, which is exactly the axis this benchmark is thin on. Cell Reports 2025.</t>
+          <t>Yeast surface display co-presenting protease mutants with their substrate, so activity is read by loss of an epitope tag under flow cytometry. A protease is in scope and the method is library-scale on its face.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS THE USER. Unpaywall reports oa_status gold with a direct PDF at https://www.cell.com/cell-reports/pdf/S2211-1247(25)01217-3.pdf, but cell.com returns 403 to automated fetches. Please download that PDF and the supplementary files. No preprint exists. Note Europe PMC records this as OPEN_ACCESS:N, inEPMC:N -- that flag is wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TEV protease engineered by enzyme-substrate co-display on yeast</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>10.1093/protein/gzaf011</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Twelfth sweep (OA filter removed)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Yeast surface display co-presenting protease mutants with their substrate, so activity is read by loss of an epitope tag under flow cytometry. A protease is in scope and the method is library-scale on its face.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>No action needed yet. PMC13010152 is already assigned but live:False -- it is under embargo and will become fetchable on its own. Re-check rather than chase.</t>
         </is>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>602323</v>
+        <v>660460</v>
       </c>
     </row>
     <row r="7">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -707,17 +707,17 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>120241</v>
+        <v>178378</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, rubisco (R. rubrum), tryptophan decarboxylase (R. gnavus), EnvZ histidine kinase (E. coli)</t>
+          <t>SpCas9 (PAMmla), RbcL, McbA, CjPglB, SaAmd, LbCas12a, YmPhytase, rubisco (R. rubrum), tryptophan decarboxylase (R. gnavus), EnvZ histidine kinase (E. coli), NucB nuclease (B. licheniformis)</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2233,26 +2233,78 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Cell Systems</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Engineering highly active nuclease enzymes with machine learning and high-throughput screening</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>10.1016/j.cels.2025.101236</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>datasets</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>58137</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>NucB, the biofilm-dispersing nuclease of Bacillus licheniformis, 142 aa, byte-identical to UniProt F1BV52. Four generations of a machine-learning-guided design campaign (TeleProt), one dataset each, read out as droplet-sort enrichment factors: g1 9,440 / g2 14,677 / g3 18,617 / g4 15,403 variants, 1-23 substitutions each. Curated from the public GCS bucket behind github.com/google-deepmind/nuclease_design, not the article, which cell.com will not serve to an automated fetch. The union of the four is 55,759 distinct genotypes, exactly reproducing the 55,760-row landscape.csv the paper headlines as 'a dataset of 55,000 nuclease variants' -- but with continuous enrichment factors in place of that file's four-level ordinal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="10">
-        <f>SUM(H2:H23)</f>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="10">
+        <f>SUM(H2:H24)</f>
         <v/>
       </c>
-      <c r="I24" s="10">
-        <f>SUM(I2:I23)</f>
+      <c r="I25" s="10">
+        <f>SUM(I2:I24)</f>
         <v/>
       </c>
-      <c r="J24" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3952,7 +4004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5343,6 +5395,48 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Thomas 2025 (NucB TeleProt campaign)</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>10.1016/j.cels.2025.101236</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>The other sort gates of each generation, and processed_data/landscape.csv</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Each generation was sorted at several stringencies and the gates are not equivalent. The most stringent recover almost nothing: g3's 99th-percentile gate is zero for 16,530 of 18,618 variants and g4's 99.5th for 14,027 of 15,404, and neither separates the variants the deposit labels as beating wild type. One gate per generation was shipped -- the one with the fewest zeros and most distinct values that still separates those labels -- and the rest left unshipped rather than averaged, since a mean across stringencies is not a quantity the experiment measured. landscape.csv, the 55,760-row summary, is excluded because its activity_level is a four-level ordinal carrying far less information per variant than the enrichment factors; its genotype set is fully covered by the four files shipped.</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>n/a -- found on curation 2026-09-07</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>Revisit the discarded gates only if a use emerges for per-stringency replicates. The raw per-bin read counts are also available in the same bucket (100 MB - 1.2 GB per file).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5355,7 +5449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5406,12 +5500,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Nuclease activity landscape, 55,000 variants (TeleProt)</t>
+          <t>TEV protease engineered by enzyme-substrate co-display on yeast</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.cels.2025.101236</t>
+          <t>10.1093/protein/gzaf011</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -5421,42 +5515,10 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>The abstract states the authors 'released a dataset of 55,000 nuclease variants, one of the most extensive genotype-phenotype enzyme activity landscapes to date'. A nuclease is in the enzyme scope, the readout is catalytic activity, and 55,000 would be among the largest datasets in this repository. Cell Systems 2025, Google Research; a bioRxiv preprint exists at 10.1101/2024.03.21.585615.</t>
+          <t>Yeast surface display co-presenting protease mutants with their substrate, so activity is read by loss of an epitope tag under flow cytometry. A protease is in scope and the method is library-scale on its face.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS THE USER. The paper is CC-BY per Crossref and Unpaywall (oa_status hybrid), so it is free -- but cell.com returns 403 to any automated fetch, and so does biorxiv.org. Please download the article PDF and its supplementary/STAR Methods from https://www.cell.com/cell-systems/pdf/S2405-4712(25)00069-9.pdf and drop them in. The data availability statement is what is actually needed: it should name where the 55,000 variants live.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>TEV protease engineered by enzyme-substrate co-display on yeast</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>10.1093/protein/gzaf011</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Twelfth sweep (OA filter removed)</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Yeast surface display co-presenting protease mutants with their substrate, so activity is read by loss of an epitope tag under flow cytometry. A protease is in scope and the method is library-scale on its face.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>No action needed yet. PMC13010152 is already assigned but live:False -- it is under embargo and will become fetchable on its own. Re-check rather than chase.</t>
         </is>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -2317,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3990,6 +3990,114 @@
       <c r="E66" s="11" t="inlineStr">
         <is>
           <t>Worked up in full on 2026-09-07 and rejected on shape, not on data quality. Supplementary Data 2 (mmc2.xls) is genuine deep-sequencing data -- five sheets, one per enzyme, each with seven condition blocks (ampicillin, carbenicillin, meropenem, ceftriaxone, clavulanic acid, sulbactam, avibactam) in three replicates, carrying raw unselected and selected counts, averaged relative fitness, errors and significance calls. But every block saturates the same single position, Ambler 105, so it would become 35 datasets of 15-19 substitutions each, 651 variant rows in total, mean 18.6, none reaching this branch's 20-variant floor: BlaC 19/17/19/19/19/19/19, CTX-M-14 19 x7, KPC-2 16/17/19/19/19/16/15, NmcA 19 x7, TEM-1 19 x7 (the shortfalls are real -- fitness is undefined where the selected count is zero). Three reasons beyond the count. A one-position scan is a 20-way ranking at one site rather than a fitness landscape, and the sequence column would make it indistinguishable from a real DMS. 35 files would be 22% of the repository's dataset count for 0.11% of its variants, distorting every per-dataset figure in the Summary tab. And Ambler 105 is a structural-alignment number rather than a sequence index, so Phase 3 would be five separate alignments, each an opportunity to place the substitution on the wrong residue. Revisit only if the floor is ever redefined as 'genuine deep-sequencing data' rather than library-scale coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>ACE2 droplet-microfluidic activity screen</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>10.1186/s13036-025-00482-3</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Thirteenth sweep (droplet / ultrahigh-throughput axis)</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Rejected on reproducibility, having been opened in full. Additional File 3 is a real machine-readable table -- 622 single substitutions in human ACE2, positions 19-614, with log enrichment values from each of three droplet sorts -- and ACE2 is a peptidase, so the enzyme scope admits it. But the three sorts do not agree: Pearson r is 0.074 between sorts 1 and 2, 0.006 between 1 and 3, and -0.029 between 2 and 3. Three sorts of one library correlating at zero means the per-variant numbers are not a measurement. The spread of the per-variant means is 1.17x the median within-variant scatter, so averaging does not rescue it either. The paper is candid about this -- it reports 'large variability in mutational enrichment across the three replicates' and uses the columns as a consensus filter to pick six mutants rather than as a landscape; those six duly rank high by mean, but they were chosen from these same three columns, so that is not independent support. 24 of the 622 labels are nonsense variants and would need dropping regardless. A dataset built from this would pass every validator here and be noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Directed evolution of a TNA polymerase</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-67652-1</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Thirteenth sweep (fitness landscape / epistasis axis)</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>Chased to the data availability statement. Source Data covers figures, kinetics and thermostability of the evolved champions, and the deposits are crystal structures (PDB 9OAT, 9OAU, 9OAV, 9OAW, 9OAX, 9OAY). No per-variant table; the one-champion directed-evolution pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Bacterial P450 steroid side-chain cleavage enzymes</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-67278-3</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Thirteenth sweep (ASR / iterative saturation axis)</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>An enzyme discovery paper, not a variant library: a BLAST and phylogenetic survey identifying CYP204 family members, with structures, docking and MD. The figshare deposit holds RESP fitting and MD simulation inputs. Homolog panel, so no shared wild type and no mutant column, the shape that also sank the Cas12a orthologs and the PET hydrolase panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Microfluidic ultrahigh-throughput ketoreductase screen</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>10.1021/acs.analchem.5c01029</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Thirteenth sweep (droplet / ultrahigh-throughput axis)</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>A discovery screen over natural ketoreductase diversity rather than a mutant library of one parent, and the full text carries no data availability statement. Same shape as the P450 paper above.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>660460</v>
+        <v>660856</v>
       </c>
     </row>
     <row r="7">
@@ -749,17 +749,17 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>147603</v>
+        <v>147999</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>RNA Pol II Rpb1 (S. cerevisiae), DAOx (Rhodotorula gracilis)</t>
+          <t>RNA Pol II Rpb1 (S. cerevisiae), DAOx (Rhodotorula gracilis), MthUPO peroxygenase (M. thermophila)</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2285,26 +2285,78 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Munch</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ACS Catalysis</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Computationally Designed Peroxygenases That Exhibit Diverse and Selective Terpene Oxyfunctionalization</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c02412</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>datasets</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>MthUPO, the unspecific peroxygenase of Myceliophthora thermophila, 245-aa expression construct. Fifty FuncLib-designed active-site variants, four substitutions each among ten designed positions, screened against eight terpene substrates -- geraniol, nerol, (R)- and (S)-limonene, alpha- and delta-damascone, alpha- and beta-ionone -- one dataset per substrate, readout being total product relative to wild type. Data from the authors' Harvard Dataverse deposit 10.7910/DVN/ZPKEAI (CC0). Found only on re-auditing ACS Catalysis with a looser query: the seventh sweep's directed-evolution vocabulary misses computational design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="10">
-        <f>SUM(H2:H24)</f>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="10">
+        <f>SUM(H2:H25)</f>
         <v/>
       </c>
-      <c r="I25" s="10">
-        <f>SUM(I2:I24)</f>
+      <c r="I26" s="10">
+        <f>SUM(I2:I25)</f>
         <v/>
       </c>
-      <c r="J25" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4112,7 +4164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5542,6 +5594,48 @@
       <c r="H40" s="16" t="inlineStr">
         <is>
           <t>Revisit the discarded gates only if a use emerges for per-stringency replicates. The raw per-bin read counts are also available in the same bucket (100 MB - 1.2 GB per file).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Munch 2025 (MthUPO FuncLib designs)</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c02412</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>The ABTS, DMP and NBD model-substrate screens; the splitGFP screen; the per-product selectivity fractions</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>The three model-substrate screens are keyed by microplate well (A1, B7, ...) rather than by design, so mapping them to variants needs the plate-scheme cross-walk in the same workbook; not attempted, and a wrong cross-walk would mislabel every row silently. splitGFP measures expression, not activity. The regio- and stereoselectivity fractions beside each substrate's activity are a different quantity and would want their own directory -- they are the paper's most striking result (regioselectivity for 3-hydroxy-beta-damascone rising from 3% to 46%), so this is the more interesting omission of the two.</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>n/a -- found on curation 2026-09-07</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>The selectivity fractions are the obvious follow-up if a Selectivity/Regioselectivity directory is ever wanted; datasets/Selectivity/ already exists for diastereoselectivity.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2369,7 +2369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4150,6 +4150,33 @@
       <c r="E70" s="11" t="inlineStr">
         <is>
           <t>A discovery screen over natural ketoreductase diversity rather than a mutant library of one parent, and the full text carries no data availability statement. Same shape as the P450 paper above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Electrostatic reactivity scoring in computer-assisted enzyme engineering (BindScan)</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>10.1111/febs.70121</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Fourteenth sweep (computational design vocabulary)</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Opened because Table S3 holds kcat, KM and kcat/KM for 51 mutants of Sf-beta-glycosidase across 37 positions, which would clear the floor. But those 51 are a benchmark dataset taken from reference [47], an earlier publication; this paper's own contribution is the BindScan metric and a 2,900-variant *virtual* saturation library that was never made. Curating it would attribute another laboratory's measurements to this DOI. The underlying reference is the thing worth chasing if single-enzyme kinetic panels are ever in scope, and it is not a 2025 paper.</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5723,6 +5750,38 @@
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>No action needed yet. PMC13010152 is already assigned but live:False -- it is under embargo and will become fetchable on its own. Re-check rather than chase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>FuncLib-stabilised Kemp eliminase (computational design + NMR hotspots)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>10.1021/jacs.4c09428</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Fourteenth sweep (computational design vocabulary)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>A designed de novo Kemp eliminase (the V4 background) with FuncLib-predicted stabilising combinations at NMR-identified catalytic hotspots. Michaelis profiles -- kcat, KM, kcat/KM -- were determined for the 20 top-ranked variants, and denaturation temperatures alongside, so there are two or three readouts on one parent. Open access, PMC12151457, with supplementary tables and a Zenodo package for the simulation inputs.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Exactly at the 20-variant floor, not above it, and the numbers live in supporting-information PDF tables rather than a machine-readable file. The combinatorial library spanned 8,000 variants and about 800 were colony-screened, but only those 20 were quantified, so the large numbers in the abstract do not translate into rows. Left open rather than rejected because it is genuinely at the boundary: worth taking only if a 20-variant designed panel with real kinetics is judged worth the extraction effort.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Yeast surface display co-presenting protease mutants with their substrate, so activity is read by loss of an epitope tag under flow cytometry. A protease is in scope and the method is library-scale on its face.</t>
+          <t>Second, independent TEV protease campaign -- and the repository already holds a verified 242-aa TEVp sequence from Huber 2025 (datasets_virus, 10.1038/s41467-025-60622-7), so Phase 3 starts half-done. Yeast surface display co-presenting protease and substrate on one Aga2 anchor: cleavage strips an N-terminal epitope tag, so activity is read as loss of fluorescent anti-tag signal and sorted by flow cytometry. Seven active-site combinatorial libraries built by saturation mutagenesis were screened, beneficial mutations pooled into a second-generation library, and that screened again. The abstract reports that 'the vast majority of resultant TEVp multi-mutants improved catalytic efficiency, generally by decreasing KM', so there is a per-variant sequence-function table behind it. Multi-mutant labels are within format scope.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>No action needed yet. PMC13010152 is already assigned but live:False -- it is under embargo and will become fetchable on its own. Re-check rather than chase.</t>
+          <t>Embargoed, with a date. PMC13010152 is assigned but the ID converter reports live=False and a release date of 2026-09-26. Unpaywall agrees it is green OA through that record and has no PDF yet; academic.oup.com returns 403 and the Europe PMC full-text and render routes 403 and 500. Nothing to chase before that date and nothing for anyone to send -- it opens by itself. Re-check on or after 2026-09-26.</t>
         </is>
       </c>
     </row>
@@ -5776,12 +5776,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>A designed de novo Kemp eliminase (the V4 background) with FuncLib-predicted stabilising combinations at NMR-identified catalytic hotspots. Michaelis profiles -- kcat, KM, kcat/KM -- were determined for the 20 top-ranked variants, and denaturation temperatures alongside, so there are two or three readouts on one parent. Open access, PMC12151457, with supplementary tables and a Zenodo package for the simulation inputs.</t>
+          <t>A FuncLib-stabilised de novo Kemp eliminase on the V4 background, a resurrected ancestral beta-lactamase scaffold. Table S5 of the supporting information gives kcat, KM, kcat/KM and a DSC denaturation temperature for every variant, so there are four candidate readouts on one parent (KM inverted). The count is better than first recorded: 20 beta-set variants plus 5 alpha-set variants plus the V4 background, so about 25 mutants rather than exactly 20. All 20 beta-set variants are more stable than V4, and catalytic efficiency spans roughly 50-fold (V4 kcat 610 s-1, best variant V4-4 at 1700 s-1).</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Exactly at the 20-variant floor, not above it, and the numbers live in supporting-information PDF tables rather than a machine-readable file. The combinatorial library spanned 8,000 variants and about 800 were colony-screened, but only those 20 were quantified, so the large numbers in the abstract do not translate into rows. Left open rather than rejected because it is genuinely at the boundary: worth taking only if a 20-variant designed panel with real kinetics is judged worth the extraction effort.</t>
+          <t>Two obstacles, one solved and one not. SOLVED: the mutations are given only as 18-digit FuncLib codes in Table S7, but Table S6 lists the allowed residues per designed position (L49 LFHIMRVWY, T51 TAMS, G58 GADEHNQST, R230 RIKMQTV, G232 GA, A248 A, W251 WFY, A257 AEGKPQRS, A262 ACSTV) and the code is two digits per position in that order -- V4's own code '010101010101010101 decodes to the original residue at all nine positions, which confirms the scheme. NOT SOLVED: no protein sequence appears anywhere in the article or its 82-page supporting information, and V4 is itself a previously designed variant, so the parent sequence has to be chased to the earlier publication that produced it and the nine positions verified against it before a sequence column can be written. That chase, plus extracting four readouts from PDF tables, is the whole cost of ~25 variants.</t>
         </is>
       </c>
     </row>

--- a/FitnessBench_2025_literature_search.xlsx
+++ b/FitnessBench_2025_literature_search.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1753,8 +1753,10 @@
           <t>Wysocki</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
-        <v>2026</v>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
@@ -2369,7 +2371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4177,6 +4179,60 @@
       <c r="E71" s="11" t="inlineStr">
         <is>
           <t>Opened because Table S3 holds kcat, KM and kcat/KM for 51 mutants of Sf-beta-glycosidase across 37 positions, which would clear the floor. But those 51 are a benchmark dataset taken from reference [47], an earlier publication; this paper's own contribution is the BindScan metric and a 2,900-variant *virtual* saturation library that was never made. Curating it would attribute another laboratory's measurements to this DOI. The underlying reference is the thing worth chasing if single-enzyme kinetic panels are ever in scope, and it is not a 2025 paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>TEV protease by enzyme-substrate co-display on yeast (Mikolajczyk 2025, PEDS)</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>10.1093/protein/gzaf011</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Closed by decision, 2026-09-08</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>Closed by decision on 2026-09-08, not on evidence -- the data was never assessed because it is embargoed. PMC13010152 is assigned with live=False and a release date of 2026-09-26. The campaign is real: seven active-site saturation libraries screened by a yeast display that co-presents protease and substrate on one Aga2 anchor, a pooled second-generation library, and an abstract reporting that most resulting multi-mutants improved catalytic efficiency by lowering KM. A verified 242-aa TEVp sequence already sits in datasets_virus from Huber 2025, so Phase 3 would start half-done. Reopen after 2026-09-26 if a second independent TEVp campaign is wanted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>FuncLib-stabilised de novo Kemp eliminase (JACS 2025)</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>10.1021/jacs.4c09428</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Closed by decision, 2026-09-08</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Closed by decision on 2026-09-08. Worked up fully first: Table S5 gives kcat, KM, kcat/KM and a DSC denaturation temperature for 20 beta-set and 5 alpha-set variants on the V4 background, so about 25 mutants and four candidate readouts -- above the floor, not at it. The FuncLib codes in Table S7 decode against the allowed sequence space in Table S6 (L49 LFHIMRVWY, T51 TAMS, G58 GADEHNQST, R230 RIKMQTV, G232 GA, A248 A, W251 WFY, A257 AEGKPQRS, A262 ACSTV), and V4's own code maps to the original residue at all nine positions, which confirms the scheme. What stops it is Phase 3: no protein sequence appears anywhere in the article or its 82-page supporting information, and V4 is itself a previously designed variant on a resurrected ancestral beta-lactamase scaffold, so the parent would have to be chased to an earlier publication and the nine positions verified against it. That cost, plus four readouts out of PDF tables, was judged not worth ~25 variants.</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5721,70 +5777,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>TEV protease engineered by enzyme-substrate co-display on yeast</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>10.1093/protein/gzaf011</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Twelfth sweep (OA filter removed)</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Second, independent TEV protease campaign -- and the repository already holds a verified 242-aa TEVp sequence from Huber 2025 (datasets_virus, 10.1038/s41467-025-60622-7), so Phase 3 starts half-done. Yeast surface display co-presenting protease and substrate on one Aga2 anchor: cleavage strips an N-terminal epitope tag, so activity is read as loss of fluorescent anti-tag signal and sorted by flow cytometry. Seven active-site combinatorial libraries built by saturation mutagenesis were screened, beneficial mutations pooled into a second-generation library, and that screened again. The abstract reports that 'the vast majority of resultant TEVp multi-mutants improved catalytic efficiency, generally by decreasing KM', so there is a per-variant sequence-function table behind it. Multi-mutant labels are within format scope.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Embargoed, with a date. PMC13010152 is assigned but the ID converter reports live=False and a release date of 2026-09-26. Unpaywall agrees it is green OA through that record and has no PDF yet; academic.oup.com returns 403 and the Europe PMC full-text and render routes 403 and 500. Nothing to chase before that date and nothing for anyone to send -- it opens by itself. Re-check on or after 2026-09-26.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>FuncLib-stabilised Kemp eliminase (computational design + NMR hotspots)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>10.1021/jacs.4c09428</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Fourteenth sweep (computational design vocabulary)</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>A FuncLib-stabilised de novo Kemp eliminase on the V4 background, a resurrected ancestral beta-lactamase scaffold. Table S5 of the supporting information gives kcat, KM, kcat/KM and a DSC denaturation temperature for every variant, so there are four candidate readouts on one parent (KM inverted). The count is better than first recorded: 20 beta-set variants plus 5 alpha-set variants plus the V4 background, so about 25 mutants rather than exactly 20. All 20 beta-set variants are more stable than V4, and catalytic efficiency spans roughly 50-fold (V4 kcat 610 s-1, best variant V4-4 at 1700 s-1).</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Two obstacles, one solved and one not. SOLVED: the mutations are given only as 18-digit FuncLib codes in Table S7, but Table S6 lists the allowed residues per designed position (L49 LFHIMRVWY, T51 TAMS, G58 GADEHNQST, R230 RIKMQTV, G232 GA, A248 A, W251 WFY, A257 AEGKPQRS, A262 ACSTV) and the code is two digits per position in that order -- V4's own code '010101010101010101 decodes to the original residue at all nine positions, which confirms the scheme. NOT SOLVED: no protein sequence appears anywhere in the article or its 82-page supporting information, and V4 is itself a previously designed variant, so the parent sequence has to be chased to the earlier publication that produced it and the nine positions verified against it before a sequence column can be written. That chase, plus extracting four readouts from PDF tables, is the whole cost of ~25 variants.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5796,7 +5788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5935,6 +5927,134 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>LetA intermembrane lipid transporter DMS</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>10.1038/s41586-025-09990-0</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Nature 2026; preprint 10.1101/2025.03.21.644421 (2025)</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Found in the MaveDB sweep, not the literature sweeps. urn:mavedb:00001252-a holds 8,967 variants of E. coli LetA, already machine-readable and downloadable now -- no chase needed. Two cautions. The scope: LetA is a lipid transporter, and the enzyme scope admits transporters only when they are ATP-driven, which needs checking. And the year is genuinely ambiguous -- a 2025 preprint with a 2026 Nature version of record, so it is invisible to a 2025 branch that excludes preprints and to a 2026 branch that indexes by preprint year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>PqiC lipoprotein DMS</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>10.64898/2026.05.09.724024</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>preprint, in MaveDB</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>urn:mavedb:00001273-a, 3,927 variants of E. coli PqiC, deposited 2026-05-06. Part of the Pqi intermembrane transport system rather than an enzyme, so it probably fails the scope; recorded because it is one of only three post-2023 in-scope-organism deposits in all of MaveDB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>MaveDB back-catalogue, in-scope organisms, 2009-2020</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>(various)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>2009-2020</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>MaveDB; 26 publications, 87 score sets</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>The MaveDB sweep enumerated every published score set on the 72 organisms in scope for datasets/. Nothing post-2023 beyond the rows above, but a substantial pre-2022 back-catalogue that no branch currently covers. The enzyme entries, largest first: TEM-1 beta-lactamase three times over (10.1093/molbev/msu081, 2014, 47,642 variants; 10.1016/j.cell.2015.01.035, 2015, 34,979; 10.1016/j.jmb.2019.04.030, 2019, 5,066 insertions and deletions), TEM-15/17/19 (10.1073/pnas.0901246106, 2009, 14,785), a heterologous-expression pipeline on PyKS (10.1021/acssynbio.8b00486, 2019, 5,746), SpCas9 (10.1038/s41598-017-17081-y, 2017, 4,940) and DHFR against a quality-control protease (10.7554/eLife.53476, 2020, 6,303). Non-enzyme but large: 10.1016/j.cub.2014.09.072 (536,476 variants, pairwise epistasis across a domain) and 10.1534/genetics.116.188037 (241,274, SUL1 promoter).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Mega-scale proteolysis folding-stability corpus</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>(no DOI in MaveDB)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>MaveDB; 518 score sets with no linked publication</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>The single largest block in MaveDB's in-scope holdings: 518 score sets, 949,551 variants, all deposited 2023-07-04 and all named '&lt;target&gt; trypsin digestion' / 'chymotrypsin digestion' / 'combined scores'. This is the mega-scale proteolysis dataset measuring folding free energies of small domains. Mostly not enzymes and it is folding stability rather than activity, but it is enormous and machine-readable, and it belongs to a 2023 branch. Recorded so that whoever opens one knows it is there and knows its shape before spending a sweep on it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
